--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7A29DE-E0B9-4DDF-86BA-C0083A0D1FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB3F93B-B55B-41D5-B703-0A9221A97F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3751,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4184,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4297,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>349</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>348</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>353</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4597,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4670,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>354</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>2.0258239687205015</v>
+        <v>1.9115679363188245</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4923,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5072,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>381</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>380</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5317,13 +5317,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>387</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5360,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5374,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>393</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>394</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,17 +5413,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5440,6 +5429,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -7922,7 +7922,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80 C19:M25">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -8018,7 +8018,7 @@
         <v>218642</v>
       </c>
       <c r="D4" s="294">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
@@ -8040,7 +8040,7 @@
         <v>651602</v>
       </c>
       <c r="D5" s="294">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>704769.25</v>
+        <v>443696.05000000005</v>
       </c>
       <c r="F12" s="80" t="s">
         <v>70</v>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="H27" s="209">
         <f>H32-G30</f>
-        <v>4628457.25</v>
+        <v>4367384.05</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="H29" s="209">
         <f>H27-G28</f>
-        <v>4628975.25</v>
+        <v>4367902.05</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="H32" s="209">
         <f>H35+H40</f>
-        <v>5388766.25</v>
+        <v>5127693.05</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="H35" s="221">
         <f>D12+D24</f>
-        <v>834533.45</v>
+        <v>573460.25</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="D46" s="188">
         <f>H29</f>
-        <v>4628975.25</v>
+        <v>4367902.05</v>
       </c>
       <c r="F46" s="283"/>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.0258239687205015</v>
+        <v>1.9115679363188245</v>
       </c>
       <c r="F47" s="283"/>
     </row>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB3F93B-B55B-41D5-B703-0A9221A97F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C08935C-C0BA-42B3-9270-6B4022514CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4079,7 +4079,7 @@
         <v>41</v>
       </c>
       <c r="C1" s="44">
-        <v>45754</v>
+        <v>45786</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
@@ -4129,7 +4129,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>407</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>2627.7315401999999</v>
+        <v>2650.5813796799998</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21644266614219942</v>
+        <v>0.21293704824312565</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.3476783162570317E-3</v>
+        <v>6.2929569514617121E-3</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -14081,38 +14081,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.3476783162570317E-3</v>
+        <v>6.2929569514617121E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.8231574978299985E-2</v>
+        <v>-2.7988199331935328E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-8.0898294497702139E-2</v>
+        <v>-8.0200895407204695E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.7056156351721065E-2</v>
+        <v>-1.6909120521102779E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.1120759007891595E-2</v>
+        <v>3.0852476602651148E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.610009917100587E-2</v>
+        <v>5.5616477626428233E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6710611159562322E-2</v>
+        <v>1.6566554166807471E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.6860971872578666E-3</v>
+        <v>-7.6198377287470228E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14138,31 +14138,31 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31796284636306776</v>
+        <v>-0.31522178734269651</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16869988171099856</v>
+        <v>-0.16724557238590373</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.3170596636886994E-3</v>
+        <v>-8.2453608734844863E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.943683478035684</v>
+        <v>-4.901065517018135</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.27228123918075126</v>
+        <v>-0.2699339871188482</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.4117521076440136</v>
+        <v>-0.4082025205091514</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.53670056412713296</v>
+        <v>-0.53207383512603701</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-1.1499999999999999</v>
+        <v>-1.1599999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21644266614219942</v>
+        <v>0.21293704824312565</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C08935C-C0BA-42B3-9270-6B4022514CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAF70AE-013E-4B85-9A87-6A17C5E77B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>0.9421991685622978</v>
+        <v>0.9576999852710768</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>316</v>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21293704824312565</v>
+        <v>0.21955254305698646</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>0</v>
+        <v>6970.1947987154417</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-11410</v>
+        <v>-4439.8052012845583</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-5559.9981728907442</v>
+        <v>-7302.5468725696046</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>-74185</v>
+        <v>-67214.805201284558</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>16679.994518672233</v>
+        <v>21907.640617708814</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.2929569514617121E-3</v>
+        <v>8.265220900462859E-3</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>9.1247875796194824E-2</v>
+        <v>0.11984570305671145</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>2.18 HKD</v>
+        <v>2.25 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>2.08 HKD</v>
+        <v>2.12 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>2.06 HKD</v>
+        <v>2.1 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>2.05 HKD</v>
+        <v>2.08 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.01 HKD</v>
+        <v>2.03 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>2.0700115733313686</v>
+        <v>2.1040668676405563</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>0.9421991685622978</v>
+        <v>0.9576999852710768</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>0.9421991685622978</v>
+        <v>0.9576999852710768</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>1.197923364196394</v>
+        <v>1.2176312891438406</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>1.197923364196394</v>
+        <v>1.2176312891438406</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>1.6432419261953275</v>
+        <v>1.6702761167953912</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>1.6432419261953275</v>
+        <v>1.6702761167953912</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5777,8 +5777,12 @@
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="181"/>
-      <c r="D13" s="181"/>
+      <c r="C13" s="181">
+        <v>70887</v>
+      </c>
+      <c r="D13" s="181">
+        <v>126188</v>
+      </c>
       <c r="E13" s="181"/>
       <c r="F13" s="181"/>
       <c r="G13" s="181"/>
@@ -6636,11 +6640,11 @@
       </c>
       <c r="C44" s="187">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>-761336</v>
+        <v>-832223</v>
       </c>
       <c r="D44" s="187">
         <f t="shared" si="18"/>
-        <v>-230719</v>
+        <v>-356907</v>
       </c>
       <c r="E44" s="187">
         <f t="shared" si="18"/>
@@ -6685,11 +6689,11 @@
       </c>
       <c r="C45" s="188">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>-11410</v>
+        <v>59477</v>
       </c>
       <c r="D45" s="188">
         <f t="shared" si="19"/>
-        <v>-8305</v>
+        <v>117883</v>
       </c>
       <c r="E45" s="188">
         <f t="shared" si="19"/>
@@ -6935,11 +6939,11 @@
       </c>
       <c r="C52" s="183">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
-        <v>0</v>
+        <v>70887</v>
       </c>
       <c r="D52" s="183">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>126188</v>
       </c>
       <c r="E52" s="183">
         <f t="shared" si="24"/>
@@ -7136,11 +7140,11 @@
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>-761336</v>
+        <v>-832223</v>
       </c>
       <c r="D58" s="188">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
-        <v>-230719</v>
+        <v>-356907</v>
       </c>
       <c r="E58" s="188">
         <f t="shared" si="28"/>
@@ -7590,11 +7594,11 @@
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
-        <v>2.2998409320428745</v>
+        <v>1.3317642971418326</v>
       </c>
       <c r="D71" s="101">
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D44/E44-1)</f>
-        <v>-11.046986587702492</v>
+        <v>-16.542022295767289</v>
       </c>
       <c r="E71" s="101">
         <f t="shared" si="37"/>
@@ -9783,16 +9787,16 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-11410</v>
+        <v>-4439.8052012845583</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-11410</v>
+        <v>-4439.8052012845583</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-8305</v>
+        <v>4102.8454619366621</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
@@ -9838,16 +9842,16 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>22239.992691562977</v>
+        <v>29210.187490278418</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>17893</v>
+        <v>24863.194798715442</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>-193162</v>
+        <v>-180754.15453806333</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
@@ -9893,7 +9897,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-5559.9981728907442</v>
+        <v>-7302.5468725696046</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10005,18 +10009,18 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>16679.994518672233</v>
+        <v>21907.640617708814</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>-74185</v>
+        <v>-67214.805201284558</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>-212579</v>
+        <v>-200171.15453806333</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
@@ -10113,18 +10117,18 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>16679.994518672233</v>
+        <v>21907.640617708814</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>-74185</v>
+        <v>-67214.805201284558</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>-212579</v>
+        <v>-200171.15453806333</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
@@ -10974,11 +10978,11 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>5.1460347621975071</v>
+        <v>3.7033856970286543</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>-0.10052184177012041</v>
+        <v>-0.10742215054266514</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
@@ -11112,16 +11116,16 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>0</v>
+        <v>6970.1947987154417</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>0</v>
+        <v>6970.1947987154417</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>0</v>
+        <v>12407.845461936662</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
@@ -11167,18 +11171,18 @@
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
-        <v>0</v>
+        <v>70887</v>
       </c>
       <c r="D49" s="325"/>
       <c r="E49" s="326"/>
       <c r="F49" s="325"/>
       <c r="G49" s="324">
         <f>Data!C52</f>
-        <v>0</v>
+        <v>70887</v>
       </c>
       <c r="H49" s="324">
         <f>Data!D52</f>
-        <v>0</v>
+        <v>126188</v>
       </c>
       <c r="I49" s="324">
         <f>Data!E52</f>
@@ -11224,16 +11228,16 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-11410</v>
+        <v>-4439.8052012845583</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-11410</v>
+        <v>-4439.8052012845583</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-8305</v>
+        <v>4102.8454619366621</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
@@ -11293,14 +11297,14 @@
       </c>
       <c r="C53" s="87">
         <f>G53</f>
-        <v>0</v>
+        <v>1.3975005584127318E-2</v>
       </c>
       <c r="E53" s="299" t="s">
         <v>345</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>0</v>
+        <v>1.3975005584127318E-2</v>
       </c>
       <c r="H53" s="170"/>
       <c r="I53" s="170"/>
@@ -11642,11 +11646,11 @@
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
-        <v>-761336</v>
+        <v>-832223</v>
       </c>
       <c r="H62" s="191">
         <f>Data!D58</f>
-        <v>-230719</v>
+        <v>-356907</v>
       </c>
       <c r="I62" s="191">
         <f>Data!E58</f>
@@ -11697,11 +11701,11 @@
       <c r="E63" s="302"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>-761336</v>
+        <v>-832223</v>
       </c>
       <c r="H63" s="184">
         <f t="shared" si="23"/>
-        <v>-230719</v>
+        <v>-356907</v>
       </c>
       <c r="I63" s="184">
         <f t="shared" si="23"/>
@@ -12311,18 +12315,18 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>1.1065068616032422E-2</v>
+        <v>4.3055871335697877E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1065068616032422E-2</v>
+        <v>4.3055871335697877E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>9.5705744879944314E-3</v>
+        <v>4.728065997133624E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
@@ -12368,18 +12372,18 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>2.1567663904662918E-2</v>
+        <v>2.8327145387125552E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>1.7352083501022623E-2</v>
+        <v>2.4111564983485257E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>-0.22259738822997957</v>
+        <v>-0.20829874774485152</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
@@ -12425,7 +12429,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>5.3919159761657296E-3</v>
+        <v>7.081786346781388E-3</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12540,18 +12544,18 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>1.617574792849719E-2</v>
+        <v>2.1245359040344164E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>7.1942341391793618E-2</v>
+        <v>6.5182859909330981E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.24497328766807566</v>
+        <v>0.23067464718294758</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
@@ -12647,18 +12651,18 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>1.617574792849719E-2</v>
+        <v>2.1245359040344164E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>7.1942341391793618E-2</v>
+        <v>6.5182859909330981E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.24497328766807566</v>
+        <v>0.23067464718294758</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
@@ -13019,18 +13023,18 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>0.2429437596581332</v>
+        <v>0.17483644908688745</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.0926320911980618</v>
+        <v>-1.1375525495513839</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>37.463162086818002</v>
+        <v>34.992464065723482</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
@@ -13630,11 +13634,11 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>-9.5884477994203685</v>
+        <v>-10.58277261787565</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5250001176033381</v>
+        <v>1.6195290512667515</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
@@ -13738,16 +13742,16 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>2.1567663904662918E-2</v>
+        <v>2.8327145387125552E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>1.7352083501022623E-2</v>
+        <v>2.4111564983485257E-2</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>-0.22259738822997957</v>
+        <v>-0.20829874774485152</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
@@ -14024,18 +14028,18 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.2998300636955863E-3</v>
+        <v>9.587656244536915E-3</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>-3.246631122504498E-2</v>
+        <v>-2.9415876317256544E-2</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.3033038672357446E-2</v>
+        <v>-8.760287122072305E-2</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
@@ -14081,18 +14085,18 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.2929569514617121E-3</v>
+        <v>8.265220900462859E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.7988199331935328E-2</v>
+        <v>-2.535851406660047E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-8.0200895407204695E-2</v>
+        <v>-7.5519716569588835E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
@@ -14924,7 +14928,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>16679.994518672233</v>
+        <v>21907.640617708814</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14956,7 +14960,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>208499.93148340291</v>
+        <v>273845.50772136019</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15022,7 +15026,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>4690154.1278291848</v>
+        <v>4755499.7040671417</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15050,7 +15054,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15103,7 +15107,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>2.0672421186312344</v>
+        <v>2.1004294432871107</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15138,7 +15142,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>17456.863109826627</v>
+        <v>22927.986150984863</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15150,7 +15154,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>16163.762138728356</v>
+        <v>21229.616806467464</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15160,7 +15164,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>18269.914255312593</v>
+        <v>23995.854145736514</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15172,7 +15176,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>15663.50673466443</v>
+        <v>20572.577285439398</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15182,7 +15186,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>19120.833152926603</v>
+        <v>25113.457954471374</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15194,7 +15198,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>15178.733831960481</v>
+        <v>19935.872607763817</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15204,7 +15208,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>20011.383488334912</v>
+        <v>26283.11401630432</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15216,7 +15220,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>14708.964259684186</v>
+        <v>19318.873426436563</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15226,7 +15230,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>20943.411090635982</v>
+        <v>27507.246658202934</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15238,7 +15242,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>14253.733676857197</v>
+        <v>18720.969872235772</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15248,7 +15252,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>21918.847758180211</v>
+        <v>28788.393119850305</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15260,7 +15264,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>13812.592113479996</v>
+        <v>18141.570950900201</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15270,7 +15274,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>22939.715262576767</v>
+        <v>30129.208812540193</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15282,7 +15286,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>13385.103525761722</v>
+        <v>17580.103958964446</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15292,7 +15296,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>24008.129539186466</v>
+        <v>31532.472823004497</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15304,7 +15308,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>12970.845365115205</v>
+        <v>17036.013917673507</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15314,7 +15318,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>25126.305072786381</v>
+        <v>33001.093673580872</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15326,7 +15330,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>12569.408160491328</v>
+        <v>16508.76302441736</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15336,7 +15340,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>26296.559487496157</v>
+        <v>34538.115350659325</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15348,7 +15352,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>12180.395113639741</v>
+        <v>15997.83012114307</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15798,7 +15802,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>218210.78887283284</v>
+        <v>286599.82688731077</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15810,7 +15814,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>101073.81643571805</v>
+        <v>132751.17350040015</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15821,7 +15825,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>241960.86135610071</v>
+        <v>317793.36547184177</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15842,7 +15846,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>241960.86135610071</v>
+        <v>317793.36547184177</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15872,19 +15876,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>163644.78386842809</v>
+        <v>214932.39161073393</v>
       </c>
       <c r="C56" s="124">
-        <v>208499.93148340285</v>
+        <v>273845.50772136013</v>
       </c>
       <c r="D56" s="124">
-        <v>222156.00962145126</v>
+        <v>291781.51194251317</v>
       </c>
       <c r="E56" s="124">
-        <v>236653.6465396774</v>
+        <v>310822.82631794544</v>
       </c>
       <c r="F56" s="124">
-        <v>264274.76708910544</v>
+        <v>347100.63095258689</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15893,19 +15897,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>138111.57194634757</v>
+        <v>181396.86316805036</v>
       </c>
       <c r="C57" s="124">
-        <v>208499.93148340285</v>
+        <v>273845.50772136007</v>
       </c>
       <c r="D57" s="124">
-        <v>236770.65391362851</v>
+        <v>310976.50475562562</v>
       </c>
       <c r="E57" s="124">
-        <v>271101.82055827463</v>
+        <v>356067.3385682886</v>
       </c>
       <c r="F57" s="124">
-        <v>350529.09498645249</v>
+        <v>460387.76753897907</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15914,19 +15918,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>115814.63218713648</v>
+        <v>152111.88093543128</v>
       </c>
       <c r="C58" s="124">
-        <v>208499.93148340279</v>
+        <v>273845.50772136002</v>
       </c>
       <c r="D58" s="124">
-        <v>255822.69610664935</v>
+        <v>335999.61210322619</v>
       </c>
       <c r="E58" s="124">
-        <v>321186.02157707058</v>
+        <v>421848.33599707007</v>
       </c>
       <c r="F58" s="124">
-        <v>504480.31604768231</v>
+        <v>662588.55482888664</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15935,19 +15939,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>99154.13764283112</v>
+        <v>130229.85174283449</v>
       </c>
       <c r="C59" s="124">
-        <v>208499.93148340279</v>
+        <v>273845.50772136002</v>
       </c>
       <c r="D59" s="124">
-        <v>276328.9055186818</v>
+        <v>362932.63451683585</v>
       </c>
       <c r="E59" s="124">
-        <v>381911.83984056796</v>
+        <v>501606.12016442942</v>
       </c>
       <c r="F59" s="124">
-        <v>739641.49296367459</v>
+        <v>971451.15939064755</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15956,19 +15960,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>87366.674375918024</v>
+        <v>114748.10150863045</v>
       </c>
       <c r="C60" s="124">
-        <v>208499.93148340273</v>
+        <v>273845.50772136002</v>
       </c>
       <c r="D60" s="124">
-        <v>296528.21939604427</v>
+        <v>389462.57783631247</v>
       </c>
       <c r="E60" s="124">
-        <v>449880.16399007372</v>
+        <v>590876.27053458907</v>
       </c>
       <c r="F60" s="124">
-        <v>1078171.1325270489</v>
+        <v>1416078.7444713688</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15977,19 +15981,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>79208.854230723853</v>
+        <v>104033.55410486754</v>
       </c>
       <c r="C61" s="124">
-        <v>208499.93148340273</v>
+        <v>273845.50772135996</v>
       </c>
       <c r="D61" s="124">
-        <v>315445.05585305241</v>
+        <v>414308.10486932099</v>
       </c>
       <c r="E61" s="124">
-        <v>522777.61595001485</v>
+        <v>686620.37750640651</v>
       </c>
       <c r="F61" s="124">
-        <v>1552893.2195738466</v>
+        <v>2039582.5990240611</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16039,23 +16043,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16066,23 +16070,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.0329678833324611</v>
+        <v>2.05541338356768</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.0585747265683785</v>
+        <v>2.0890456199774996</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>2.0649194700099747</v>
+        <v>2.097378857675777</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>2.0770075726741548</v>
+        <v>2.1132554701423083</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16093,23 +16097,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.0217935326572931</v>
+        <v>2.0407369004037452</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>2.0649706770979077</v>
+        <v>2.0974461134820221</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>2.0799953632339725</v>
+        <v>2.1171796585916631</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>2.1147559025794234</v>
+        <v>2.1628344340057311</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16120,23 +16124,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.0120355036003601</v>
+        <v>2.0279206255855997</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>2.0733086097165137</v>
+        <v>2.108397222074931</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>2.1019142047482129</v>
+        <v>2.1459680435106723</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>2.1821310896987818</v>
+        <v>2.2513255533708758</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16147,23 +16151,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.0047442075022461</v>
+        <v>2.0183441779209454</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>2.0822829438381958</v>
+        <v>2.1201841855838794</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>2.128490241886964</v>
+        <v>2.1808732270841369</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>2.2850469885705547</v>
+        <v>2.3864961329419501</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16174,23 +16178,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>1.9995855440126269</v>
+        <v>2.0115687472892536</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>2.091122968248452</v>
+        <v>2.1317947456242234</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>2.1582358881130554</v>
+        <v>2.2199414010414618</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>2.4332010444708954</v>
+        <v>2.5810828763061187</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16200,23 +16204,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>1.9960153569431143</v>
+        <v>2.0068796345219004</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0994017294509386</v>
+        <v>2.1426681379973975</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>2.1901387170251563</v>
+        <v>2.261842836303456</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>2.6409583407365051</v>
+        <v>2.8539530008855203</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16251,7 +16255,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.1821310896987818</v>
+        <v>2.2513255533708758</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16273,7 +16277,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.0799953632339725</v>
+        <v>2.1171796585916631</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16296,7 +16300,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.0649706770979077</v>
+        <v>2.0974461134820221</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16319,7 +16323,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16342,7 +16346,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.0120355036003601</v>
+        <v>2.0279206255855997</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16492,7 +16496,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>2.0700115733313686</v>
+        <v>2.1040668676405563</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16526,7 +16530,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>-74185</v>
+        <v>-67214.805201284558</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16548,7 +16552,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>16679.994518672233</v>
+        <v>21907.640617708814</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16632,7 +16636,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-1.968043728142399</v>
+        <v>-1.9367231569408296</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16698,7 +16702,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16745,7 +16749,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>2.0649706770979077</v>
+        <v>2.0974461134820221</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16803,7 +16807,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>2.0525982827732254</v>
+        <v>2.0811961100337415</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16861,7 +16865,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>2.0799953632339725</v>
+        <v>2.1171796585916631</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16888,7 +16892,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.0670036040737907</v>
+        <v>2.1001161763252583</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16962,7 +16966,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>2.0120355036003601</v>
+        <v>2.0279206255855997</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17020,7 +17024,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>2.1821310896987818</v>
+        <v>2.2513255533708758</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17046,7 +17050,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.0700115733313686</v>
+        <v>2.1040668676405563</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17108,7 +17112,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>2.0672421186312344</v>
+        <v>2.1004294432871107</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17171,7 +17175,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.94750697640812487</v>
+        <v>0.93217113825685383</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17243,7 +17247,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>0.9421991685622978</v>
+        <v>0.9576999852710768</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17253,7 +17257,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>0.9421991685622978</v>
+        <v>0.9576999852710768</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17294,7 +17298,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21293704824312565</v>
+        <v>0.21955254305698646</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17332,7 +17336,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.197923364196394</v>
+        <v>1.2176312891438406</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17342,7 +17346,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.197923364196394</v>
+        <v>1.2176312891438406</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17392,7 +17396,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>1.6432419261953275</v>
+        <v>1.6702761167953912</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17404,7 +17408,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>1.6432419261953275</v>
+        <v>1.6702761167953912</v>
       </c>
       <c r="D99" t="s">
         <v>407</v>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAF70AE-013E-4B85-9A87-6A17C5E77B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D34D3B3-B066-4065-AF6D-492BA5EB9124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1414,10 +1414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1579,10 +1575,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1790,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2370,13 +2358,49 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>聯易融科技</t>
+  </si>
+  <si>
     <t>9959.HK</t>
   </si>
   <si>
-    <t>聯易融科技</t>
+    <t/>
   </si>
   <si>
     <t>FIN_03</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3050,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3751,29 +3775,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4063,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4083,10 +4113,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>288</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4104,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>9959.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>424</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4115,343 +4144,335 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>428</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>2284983948</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>1.1599999999999999</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>407</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>2284983948</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>404</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>2650.5813796799998</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
-        <v>358</v>
+      <c r="B15" s="4" t="s">
+        <v>428</v>
       </c>
       <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>407</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>429</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="E19" s="339">
+      <c r="D24" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>0.9576999852710768</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E20" s="330">
+      <c r="D25" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C21" s="280">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.21955254305698646</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>33649.992691562977</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>6970.1947987154417</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>351</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-11410</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-4439.8052012845583</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4459,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>6970.1947987154417</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-11410</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-4439.8052012845583</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-7302.5468725696046</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
-        <v>348</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
+        <v>346</v>
+      </c>
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>-67214.805201284558</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>-67214.805201284558</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>21907.640617708814</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
-        <v>401</v>
-      </c>
-      <c r="C58" s="92">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
+        <v>398</v>
+      </c>
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.265220900462859E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
-        <v>317</v>
-      </c>
-      <c r="C59" s="92">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
+        <v>363</v>
+      </c>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
+        <v>370</v>
+      </c>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C72" s="311">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
-        <v>367</v>
-      </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
     <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
+        <v>372</v>
+      </c>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.11984570305671145</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
-        <v>368</v>
-      </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
+        <v>365</v>
+      </c>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>115864</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>5.0706701944848852E-2</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C88" s="337">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>9.7057481271370302E-2</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
-        <v>416</v>
-      </c>
-      <c r="C89" s="337">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>1.4790654865358754E-2</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
-        <v>418</v>
-      </c>
-      <c r="C90" s="338">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
+        <v>415</v>
+      </c>
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>3.4432102574884196</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>5072413</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>4573651.4963457817</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0016120902507897</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>23866.7</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4866,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.0445018671089587E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>4573651.4963457817</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.0016120902507897</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>2.0811961100337415</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>23866.7</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>417</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>1.9115679363188245</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.0445018671089587E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
-        <v>369</v>
-      </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>2.0811961100337415</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>2.0258239687205015</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
+        <v>366</v>
+      </c>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
+        <v>375</v>
+      </c>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.15</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>2.25 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.08</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>2.12 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>2.1 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>2.08 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.15</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>2.03 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>2.1040668676405563</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
-        <v>413</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
-        <v>379</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="B124" s="348" t="s">
+        <v>378</v>
+      </c>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
+        <v>410</v>
+      </c>
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
+        <v>377</v>
+      </c>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>0</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
-        <v>421</v>
-      </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>9959.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>0.9576999852710768</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>0.9576999852710768</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.54483386436049175</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
-        <v>424</v>
-      </c>
-      <c r="C136" s="337">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>1.2176312891438406</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>1.2176312891438406</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.42129629629629628</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
-        <v>411</v>
-      </c>
-      <c r="C142" s="92">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>1.6702761167953912</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
-        <v>412</v>
-      </c>
-      <c r="C145" s="239">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>1.6702761167953912</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>0.20616775897983042</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
+        <v>382</v>
+      </c>
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
+        <v>388</v>
+      </c>
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
-        <v>391</v>
-      </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>392</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
-        <v>399</v>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5474,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="104">
@@ -5939,7 +6065,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>711319</v>
@@ -5969,7 +6095,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-12356</v>
@@ -5999,7 +6125,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-486204</v>
@@ -6063,7 +6189,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7338,7 +7464,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8022,7 +8148,7 @@
         <v>218642</v>
       </c>
       <c r="D4" s="294">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
@@ -8044,7 +8170,7 @@
         <v>651602</v>
       </c>
       <c r="D5" s="294">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
@@ -8175,7 +8301,7 @@
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>443696.05000000005</v>
+        <v>704769.25</v>
       </c>
       <c r="F12" s="80" t="s">
         <v>70</v>
@@ -8437,7 +8563,7 @@
       </c>
       <c r="H27" s="209">
         <f>H32-G30</f>
-        <v>4367384.05</v>
+        <v>4628457.25</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
@@ -8471,7 +8597,7 @@
       </c>
       <c r="H29" s="209">
         <f>H27-G28</f>
-        <v>4367902.05</v>
+        <v>4628975.25</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
@@ -8524,7 +8650,7 @@
       </c>
       <c r="H32" s="209">
         <f>H35+H40</f>
-        <v>5127693.05</v>
+        <v>5388766.25</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
@@ -8567,7 +8693,7 @@
       </c>
       <c r="H35" s="221">
         <f>D12+D24</f>
-        <v>573460.25</v>
+        <v>834533.45</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
@@ -8715,7 +8841,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8731,7 +8857,7 @@
       </c>
       <c r="D46" s="188">
         <f>H29</f>
-        <v>4367902.05</v>
+        <v>4628975.25</v>
       </c>
       <c r="F46" s="283"/>
     </row>
@@ -8746,7 +8872,7 @@
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.9115679363188245</v>
+        <v>2.0258239687205015</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8921,7 +9047,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -8988,7 +9114,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -9000,7 +9126,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9011,12 +9137,12 @@
         <v>-83126.91727570309</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -9027,12 +9153,12 @@
         <v>61.020102347553312</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -9040,12 +9166,12 @@
         <v>498761.50365421851</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -9053,7 +9179,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9129,7 +9255,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9140,15 +9266,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>297</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9165,7 +9291,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9199,7 +9325,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9243,7 +9369,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -10070,7 +10196,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10095,7 +10221,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10423,7 +10549,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10483,7 +10609,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10607,7 +10733,7 @@
         <v>-217895.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10665,7 +10791,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10973,7 +11099,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11112,7 +11238,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11167,7 +11293,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11300,7 +11426,7 @@
         <v>1.3975005584127318E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11327,7 +11453,7 @@
         <v>9.8477525374577088E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11642,7 +11768,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11871,7 +11997,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12203,7 +12329,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>364</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12882,7 +13008,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13576,7 +13702,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13628,7 +13754,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14137,7 +14263,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14938,7 +15064,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -14948,7 +15074,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -14966,10 +15092,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -14984,8 +15110,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15000,8 +15126,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15016,8 +15142,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15043,7 +15169,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16362,7 +16488,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16434,7 +16560,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16511,11 +16637,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 聯易融科技(9959.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16536,8 +16662,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16558,8 +16684,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16569,8 +16695,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16583,8 +16709,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16602,8 +16728,8 @@
         <v>-4.8760226650597205E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16620,8 +16746,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.53605739463275559</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16638,8 +16764,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9367231569408296</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16655,7 +16781,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16665,21 +16791,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="351"/>
+      <c r="E18" s="353" t="s">
+        <v>338</v>
+      </c>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+        <v>310</v>
+      </c>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16693,8 +16819,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16708,8 +16834,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16729,8 +16855,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16740,8 +16866,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16755,8 +16881,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16766,8 +16892,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16787,8 +16913,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16798,8 +16924,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16813,8 +16939,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16824,8 +16950,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16845,8 +16971,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16856,8 +16982,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16871,8 +16997,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16883,8 +17009,8 @@
         <v>0.3</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -16946,8 +17072,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -16957,8 +17083,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -16972,8 +17098,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -16983,12 +17109,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17004,8 +17130,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17015,8 +17141,8 @@
         <v>0.15</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17030,8 +17156,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17041,8 +17167,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17057,16 +17183,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17075,10 +17201,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17091,7 +17217,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17103,7 +17229,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17119,20 +17245,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17142,19 +17268,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17164,14 +17290,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17194,7 +17320,7 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17217,15 +17343,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17276,12 +17402,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17294,7 +17420,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17306,15 +17432,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17362,17 +17488,17 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
@@ -17404,14 +17530,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>1.6702761167953912</v>
       </c>
       <c r="D99" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
@@ -17426,32 +17552,32 @@
     </row>
     <row r="101" spans="2:8" ht="14.65">
       <c r="E101" s="320" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F101" s="317"/>
     </row>
     <row r="102" spans="2:8" ht="13.9">
       <c r="E102" s="313" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F102" s="318" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="13.9">
       <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
         <v>335</v>
-      </c>
-      <c r="F103" s="318" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="13.9">
       <c r="E104" s="315" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F104" s="319" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D34D3B3-B066-4065-AF6D-492BA5EB9124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78074EAB-FD75-444F-8A59-B3D0A86059D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8576,7 +8576,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>-518</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78074EAB-FD75-444F-8A59-B3D0A86059D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479EDD73-37FD-4684-8892-B0274FDB0BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.1599999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4226,8 +4226,7 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2650.5813796799998</v>
+        <v>1</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>0.9576999852710768</v>
+        <v>0.76678821707017375</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4349,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21955254305698646</v>
+        <v>0.2058485455024226</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.265220900462859E-3</v>
+        <v>7.9897135371140952E-3</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>0.9576999852710768</v>
+        <v>0.76678821707017375</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>0.9576999852710768</v>
+        <v>0.76678821707017375</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54483386436049175</v>
+        <v>0.63556851311953344</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -14211,38 +14210,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.265220900462859E-3</v>
+        <v>7.9897135371140952E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.535851406660047E-2</v>
+        <v>-2.4513230264380455E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.5519716569588835E-2</v>
+        <v>-7.3002392683935879E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.6909120521102779E-2</v>
+        <v>-1.6345483170399352E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.0852476602651148E-2</v>
+        <v>2.9824060715896109E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5616477626428233E-2</v>
+        <v>5.3762595038880624E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6566554166807471E-2</v>
+        <v>1.6014335694580557E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.6198377287470228E-3</v>
+        <v>-7.3658431377887886E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14268,31 +14267,31 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31522178734269651</v>
+        <v>-0.30471439443127329</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16724557238590373</v>
+        <v>-0.16167071997304028</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.2453608734844863E-3</v>
+        <v>-7.9705155110350034E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.901065517018135</v>
+        <v>-4.737696666450864</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.2699339871188482</v>
+        <v>-0.26093618754821996</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.4082025205091514</v>
+        <v>-0.39459576982551303</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.53207383512603701</v>
+        <v>-0.51433804062183575</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16573,7 +16572,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-1.1599999999999999</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16813,7 +16812,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>1.1599999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17352,7 +17351,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17373,7 +17372,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>0.9576999852710768</v>
+        <v>0.76678821707017375</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17383,7 +17382,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>0.9576999852710768</v>
+        <v>0.76678821707017375</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17394,7 +17393,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.54483386436049175</v>
+        <v>0.63556851311953344</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17411,7 +17410,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>1.1599999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17424,7 +17423,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21955254305698646</v>
+        <v>0.2058485455024226</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479EDD73-37FD-4684-8892-B0274FDB0BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA12D017-B56C-4E9C-ABB3-F180427308FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <v>1</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>2741.9807375999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA12D017-B56C-4E9C-ABB3-F180427308FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88632B18-6A8E-4697-80A5-0BB879F4A8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -7369,11 +7369,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
       <c r="E62" s="183">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88632B18-6A8E-4697-80A5-0BB879F4A8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC7027-09E8-47E3-85CB-D9077747C3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC7027-09E8-47E3-85CB-D9077747C3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71941F31-30D3-401B-9C30-815808A802CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2374,6 +2374,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4194,10 +4206,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4206,7 +4218,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.2</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4239,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2741.9807375999999</v>
+        <v>2604.8817007199996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4310,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4350,10 +4362,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2058485455024226</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.22664312414291476</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4643,7 +4659,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9897135371140952E-3</v>
+        <v>8.4102247759095753E-3</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4709,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4721,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5308,7 +5324,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5318,7 +5334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5328,7 +5344,7 @@
         <v>1.2176312891438406</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
@@ -5341,7 +5357,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>425</v>
       </c>
@@ -5354,7 +5370,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
@@ -5363,12 +5379,12 @@
         <v>0.42129629629629628</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5377,7 +5393,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5387,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5397,7 +5413,7 @@
         <v>1.6702761167953912</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
@@ -5410,7 +5426,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>425</v>
       </c>
@@ -5423,7 +5439,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
@@ -5432,118 +5448,187 @@
         <v>0.20616775897983042</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>1.5081117949794698</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>1.5081117949794698</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.28199835524143158</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6189,7 +6274,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11997,7 +12082,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12329,7 +12414,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -14211,38 +14296,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9897135371140952E-3</v>
+        <v>8.4102247759095753E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.4513230264380455E-2</v>
+        <v>-2.5803400278295217E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.3002392683935879E-2</v>
+        <v>-7.6844623877827242E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.6345483170399352E-2</v>
+        <v>-1.720577175831511E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.9824060715896109E-2</v>
+        <v>3.1393748121995906E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.3762595038880624E-2</v>
+        <v>5.6592205304084868E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6014335694580557E-2</v>
+        <v>1.6857195467979532E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.3658431377887886E-3</v>
+        <v>-7.7535190924092508E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14268,31 +14353,31 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30471439443127329</v>
+        <v>-0.32075199413818239</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16167071997304028</v>
+        <v>-0.17017970523477924</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-7.9705155110350034E-3</v>
+        <v>-8.390016327405268E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.737696666450864</v>
+        <v>-4.9870491225798563</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.26093618754821996</v>
+        <v>-0.27466967110338941</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.39459576982551303</v>
+        <v>-0.41536396823738214</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.51433804062183575</v>
+        <v>-0.54140846381245877</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16540,7 +16625,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16573,7 +16658,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-1.2</v>
+        <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16813,7 +16898,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>1.2</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17411,7 +17496,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>1.2</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17424,7 +17509,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2058485455024226</v>
+        <v>0.22664312414291476</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17550,33 +17635,89 @@
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>1.5081117949794698</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>1.5081117949794698</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.28199835524143158</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71941F31-30D3-401B-9C30-815808A802CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01930AF9-4A55-43FC-8BF4-BE9C96954B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2379,13 +2356,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>Y</t>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,6 +3803,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45786</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>434</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>435</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4271,29 +4307,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>404</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>448</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>438</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>0.76678821707017375</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>2.1040668676405563</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.22664312414291476</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>9959.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>0.76678821707017375</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>427</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>1.2176312891438406</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>1.6702761167953912</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>1.5081117949794698</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>33649.992691562977</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>6970.1947987154417</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>6970.1947987154417</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-11410</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-4439.8052012845583</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-7302.5468725696046</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,20 +4676,16 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="str">
@@ -4609,1059 +4693,1092 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>-67214.805201284558</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-7302.5468725696046</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>21907.640617708814</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>-67214.805201284558</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>21907.640617708814</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.4102247759095753E-3</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.11984570305671145</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>115864</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>5.0706701944848852E-2</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>9.7057481271370302E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>1.4790654865358754E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>3.4432102574884196</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>5072413</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>4573651.4963457817</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0016120902507897</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>23866.7</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.0445018671089587E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>4573651.4963457817</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.0016120902507897</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>2.0811961100337415</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>23866.7</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>2.0258239687205015</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.0445018671089587E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>2.0811961100337415</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>2.0258239687205015</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.15</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>2.25 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.08</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>2.12 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>2.1 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>2.08 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.15</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>2.03 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>2.1040668676405563</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>0</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>9959.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>0.76678821707017375</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>0.76678821707017375</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C140" s="340" t="str">
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.63556851311953344</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>1.2176312891438406</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>1.2176312891438406</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C148" s="340" t="str">
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.42129629629629628</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>1.6702761167953912</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>1.6702761167953912</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C156" s="340" t="str">
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>0.20616775897983042</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>1.5081117949794698</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>1.5081117949794698</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C164" s="340" t="str">
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>0.28199835524143158</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5675,17 +5792,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="104">
@@ -6150,7 +6267,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>711319</v>
@@ -6180,7 +6297,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-12356</v>
@@ -6210,7 +6327,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-486204</v>
@@ -6274,7 +6391,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7549,7 +7666,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7997,11 +8114,11 @@
         <f t="shared" si="40"/>
         <v>152761</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8031,11 +8148,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8167,15 +8284,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8232,7 +8349,7 @@
       <c r="C4" s="19">
         <v>218642</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8242,7 +8359,7 @@
       <c r="G4" s="19">
         <v>4898385</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8254,7 +8371,7 @@
         <f>171505+458442+21655</f>
         <v>651602</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8264,7 +8381,7 @@
       <c r="G5" s="19">
         <v>174028</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8275,7 +8392,7 @@
       <c r="C6" s="19">
         <v>0</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8285,7 +8402,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8296,7 +8413,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8306,7 +8423,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8317,7 +8434,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8327,7 +8444,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8338,7 +8455,7 @@
       <c r="C9" s="19">
         <v>1813746</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8348,7 +8465,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8359,10 +8476,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8371,10 +8488,10 @@
       <c r="C11" s="19">
         <v>24965</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8432,7 +8549,7 @@
       <c r="C15" s="19">
         <v>4743</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8441,7 +8558,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8452,7 +8569,7 @@
       <c r="C16" s="19">
         <v>102771</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8461,7 +8578,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8472,7 +8589,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8481,7 +8598,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8492,7 +8609,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8501,7 +8618,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8513,7 +8630,7 @@
         <f>28675+74147</f>
         <v>102822</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8522,7 +8639,7 @@
       <c r="G19" s="19">
         <v>238667</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8533,7 +8650,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8542,7 +8659,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8553,7 +8670,7 @@
       <c r="C21" s="19">
         <v>276368</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8562,7 +8679,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8573,10 +8690,10 @@
       <c r="C22" s="19">
         <v>58201</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8586,10 +8703,10 @@
         <f>28964</f>
         <v>28964</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8922,13 +9039,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8944,7 +9061,7 @@
         <f>H29</f>
         <v>4628975.25</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -8959,23 +9076,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>2.0258239687205015</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -8989,7 +9106,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.9539978841756818</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9000,22 +9117,22 @@
         <f>G29/G32</f>
         <v>0.91158954067906739</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9029,7 +9146,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>8.9261562605853981E-3</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9043,22 +9160,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9080,22 +9197,22 @@
         <f>G39/G32</f>
         <v>1.1964527413850562E-2</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9109,7 +9226,7 @@
         <f>G28/G29</f>
         <v>-6.6121078416918412E-5</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9128,13 +9245,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9162,7 +9279,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9172,7 +9289,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9182,7 +9299,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9192,26 +9309,26 @@
         <f>SUM(C66:C69)</f>
         <v>5072413</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9222,65 +9339,65 @@
         <v>-83126.91727570309</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>60.75534350764071</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>61.020102347553312</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>498761.50365421851</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>6</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9294,7 +9411,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9308,7 +9425,7 @@
         <f>G19*H19</f>
         <v>23866.7</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9322,7 +9439,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9336,11 +9453,11 @@
         <f>SUM(D79:D81)</f>
         <v>23866.7</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9351,15 +9468,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9369,14 +9486,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-5.0706701944848852E-2</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9386,13 +9503,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>2.0016120902507897</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9403,24 +9520,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.0445018671089587E-2</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>4481654.1963457819</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>1.9613504069770304</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9439,22 +9556,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9541,7 +9658,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9555,7 +9672,7 @@
         <v>1031173</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9611,7 +9728,7 @@
         <f>C25</f>
         <v>-448336.00730843702</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-462912</v>
@@ -9666,7 +9783,7 @@
         <f>C4+C5</f>
         <v>582836.99269156298</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>568261</v>
@@ -9721,7 +9838,7 @@
         <f>C35</f>
         <v>-549187</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-538958</v>
@@ -9777,7 +9894,7 @@
         <v>33649.992691562977</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9833,7 +9950,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -9888,7 +10005,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -9944,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10000,7 +10117,7 @@
         <f>C50</f>
         <v>-4439.8052012845583</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-4439.8052012845583</v>
@@ -10055,7 +10172,7 @@
         <f>SUM(C8:C12)</f>
         <v>29210.187490278418</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>24863.194798715442</v>
@@ -10110,7 +10227,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-7302.5468725696046</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-92078</v>
@@ -10166,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10223,7 +10340,7 @@
         <v>21907.640617708814</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10280,8 +10397,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10305,8 +10422,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10331,7 +10448,7 @@
         <v>21907.640617708814</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10427,7 +10544,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10451,7 +10568,7 @@
         <v>-295465.98495177622</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10508,7 +10625,7 @@
         <v>-152870.0223566608</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10565,7 +10682,7 @@
         <v>-448336.00730843702</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10614,14 +10731,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10633,8 +10750,8 @@
         <v>0.28653386478483844</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10693,8 +10810,8 @@
         <v>0.14824866667054007</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10751,7 +10868,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.43478253145537848</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.44891788283828221</v>
@@ -10799,14 +10916,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10817,8 +10934,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-217895.5</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10875,8 +10992,8 @@
         <v>-331291.5</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10934,7 +11051,7 @@
         <v>-549187</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -10983,14 +11100,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11003,7 +11120,7 @@
         <v>0.21130838375325964</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11061,7 +11178,7 @@
         <v>0.32127635227066653</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11117,7 +11234,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.5325847360239262</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.52266496504466275</v>
@@ -11165,26 +11282,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11263,7 +11380,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11274,7 +11391,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-11410</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-11410</v>
@@ -11323,111 +11440,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>6970.1947987154417</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>6970.1947987154417</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>12407.845461936662</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="328" t="str">
+      <c r="N48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="328" t="str">
+      <c r="O48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="328" t="str">
+      <c r="P48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>70887</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>70887</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>126188</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="324" t="str">
+      <c r="N49" s="320" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="324" t="str">
+      <c r="O49" s="320" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="324" t="str">
+      <c r="P49" s="320" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11441,7 +11558,7 @@
         <f>C47+C48</f>
         <v>-4439.8052012845583</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-4439.8052012845583</v>
@@ -11489,14 +11606,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11510,8 +11627,8 @@
         <f>G53</f>
         <v>1.3975005584127318E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11537,8 +11654,8 @@
         <f>G54</f>
         <v>9.8477525374577088E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11564,7 +11681,7 @@
         <f>-C8/C47</f>
         <v>2.9491667564910586</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>2.5681858019281334</v>
@@ -11612,14 +11729,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11633,7 +11750,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11688,7 +11805,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11743,7 +11860,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11798,7 +11915,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11849,11 +11966,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11909,7 +12026,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-832223</v>
@@ -11957,14 +12074,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -11978,7 +12095,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12003,7 +12120,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12028,7 +12145,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12054,7 +12171,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12082,7 +12199,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12104,7 +12221,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12128,7 +12245,7 @@
         <v>0.43478253145537848</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12185,7 +12302,7 @@
         <v>0.56521746854462152</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12242,7 +12359,7 @@
         <v>0.5325847360239262</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12299,7 +12416,7 @@
         <v>3.2632732520695339E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12356,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12413,8 +12530,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>442</v>
+      <c r="E78" s="296" t="s">
+        <v>452</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12472,7 +12589,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12529,7 +12646,7 @@
         <v>4.3055871335697877E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12586,7 +12703,7 @@
         <v>2.8327145387125552E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12643,7 +12760,7 @@
         <v>7.081786346781388E-3</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12696,12 +12813,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12758,7 +12875,7 @@
         <v>2.1245359040344164E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12810,26 +12927,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12839,7 +12956,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12865,7 +12982,7 @@
         <v>2.1245359040344164E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12914,14 +13031,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -12933,7 +13050,7 @@
         <f>G90</f>
         <v>0</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0</v>
@@ -12989,7 +13106,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>0</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>0</v>
@@ -13044,7 +13161,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0</v>
@@ -13093,13 +13210,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>0</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>0</v>
@@ -13147,7 +13264,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13156,7 +13273,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13180,7 +13297,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13237,7 +13354,7 @@
         <v>0.17483644908688745</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13315,7 +13432,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13330,7 +13447,7 @@
         <v>8593904</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13387,7 +13504,7 @@
         <v>218642</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13444,7 +13561,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13501,7 +13618,7 @@
         <v>760309</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13558,7 +13675,7 @@
         <v>7833595</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13607,7 +13724,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13616,7 +13733,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13642,7 +13759,7 @@
         <v>0.2120323165947906</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13699,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13756,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13775,63 +13892,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>-0.85134784164611066</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.7312981335354547</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>-85.089361702127661</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>5.6289616404015405E-2</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>-2.9349096133795118</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>-0.18653220872220588</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>0.70290185456337462</v>
       </c>
-      <c r="N113" s="334" t="str">
+      <c r="N113" s="329" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="334" t="str">
+      <c r="O113" s="329" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="334" t="str">
+      <c r="P113" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13839,58 +13956,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>-10.58277261787565</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6195290512667515</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>-41.491956536290409</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-8.9418785233011722</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>14.244552830086286</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>4.5961831887226436</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>49.081843838193791</v>
       </c>
-      <c r="N114" s="334" t="str">
+      <c r="N114" s="329" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="334" t="str">
+      <c r="O114" s="329" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="334" t="str">
+      <c r="P114" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13899,7 +14016,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -13955,7 +14072,7 @@
         <f>C81</f>
         <v>2.8327145387125552E-2</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>2.4111564983485257E-2</v>
@@ -14009,7 +14126,7 @@
         <f>C4/C101</f>
         <v>0.11998888979909481</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.11998888979909481</v>
@@ -14064,7 +14181,7 @@
         <v>1.0970574812713703</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14121,7 +14238,7 @@
         <v>4.2956002565313857E-3</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14217,7 +14334,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14242,7 +14359,7 @@
         <v>9.587656244536915E-3</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14299,7 +14416,7 @@
         <v>8.4102247759095753E-3</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14348,7 +14465,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15099,13 +15216,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15149,7 +15266,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15159,7 +15276,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15177,10 +15294,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15195,8 +15312,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15211,8 +15328,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15227,8 +15344,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15292,7 +15409,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15302,7 +15419,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15312,7 +15429,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16573,7 +16690,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16626,12 +16743,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16644,19 +16761,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-1.1399999999999999</v>
       </c>
@@ -16673,19 +16790,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -16699,13 +16816,13 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>2.1040668676405563</v>
       </c>
@@ -16722,15 +16839,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 聯易融科技(9959.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16747,12 +16864,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16769,37 +16886,37 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16813,12 +16930,12 @@
         <v>-4.8760226650597205E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16831,12 +16948,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.53605739463275559</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16849,8 +16966,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9367231569408296</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16866,7 +16983,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16876,25 +16993,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16904,12 +17021,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16919,8 +17036,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16940,8 +17057,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16951,8 +17068,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16966,8 +17083,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16977,8 +17094,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16998,8 +17115,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17009,8 +17126,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17024,8 +17141,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17035,8 +17152,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17056,8 +17173,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17067,8 +17184,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17082,8 +17199,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17094,8 +17211,8 @@
         <v>0.3</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17157,8 +17274,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17168,8 +17285,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17183,8 +17300,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17194,12 +17311,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17215,8 +17332,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17226,8 +17343,8 @@
         <v>0.15</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17241,8 +17358,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17252,8 +17369,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17268,16 +17385,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17286,10 +17403,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17301,8 +17418,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17313,8 +17430,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17329,23 +17446,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17353,38 +17470,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>0.93217113825685383</v>
       </c>
@@ -17404,10 +17521,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17428,15 +17545,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17477,7 +17594,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.63556851311953344</v>
       </c>
@@ -17487,14 +17604,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>1.1399999999999999</v>
       </c>
@@ -17505,9 +17622,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.22664312414291476</v>
       </c>
@@ -17517,15 +17634,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17566,28 +17683,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.42129629629629628</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17599,7 +17716,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17611,23 +17728,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>1.6702761167953912</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>0.20616775897983042</v>
       </c>
@@ -17637,15 +17754,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17671,19 +17788,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>1.5081117949794698</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>0.28199835524143158</v>
       </c>
@@ -17692,33 +17809,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01930AF9-4A55-43FC-8BF4-BE9C96954B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E171D08-7EA9-42AB-9CAD-493C8C51D370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,29 +3830,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4312,13 +4312,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>1.2176312891438406</v>
+        <v>1.1661640402286717</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4458,7 +4458,7 @@
         <v>440</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4514,22 +4514,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4541,13 +4541,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4567,13 +4567,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4602,13 +4602,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4738,22 +4738,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4814,22 +4814,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4873,22 +4873,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4944,13 +4944,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5081,13 +5081,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5126,13 +5126,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5275,13 +5275,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,22 +5294,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>1.2176312891438406</v>
+        <v>1.1661640402286717</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>1.2176312891438406</v>
+        <v>1.1661640402286717</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.42129629629629628</v>
+        <v>0.44575713910823733</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5642,13 +5642,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5685,13 +5685,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5699,22 +5699,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,17 +5738,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5765,6 +5754,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.2176312891438406</v>
+        <v>1.1661640402286717</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.2176312891438406</v>
+        <v>1.1661640402286717</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.42129629629629628</v>
+        <v>0.44575713910823733</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E171D08-7EA9-42AB-9CAD-493C8C51D370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB926A8-63C5-4318-BD12-EC32ADAE1DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3111,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3745,7 +3745,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3809,9 +3808,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3830,29 +3826,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4160,7 +4166,7 @@
         <v>45786</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4194,7 +4200,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>445</v>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       <c r="D22" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>442</v>
       </c>
     </row>
@@ -4378,7 +4384,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4388,14 +4394,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>2.1040668676405563</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.22664312414291476</v>
       </c>
@@ -4408,18 +4414,18 @@
       <c r="B28" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>9959.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4427,18 +4433,18 @@
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>0.76678821707017375</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>427</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4446,18 +4452,18 @@
       <c r="B30" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>1.1661640402286717</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4465,18 +4471,18 @@
       <c r="B31" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>1.6702761167953912</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>439</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4484,18 +4490,18 @@
       <c r="B32" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>1.5081117949794698</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4523,13 +4529,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4636,7 +4642,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>6970.1947987154417</v>
       </c>
@@ -4644,14 +4650,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-11410</v>
       </c>
@@ -4659,8 +4665,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4719,10 +4725,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4823,13 +4829,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4867,7 +4873,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4979,28 +4985,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>9.7057481271370302E-2</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>1.4790654865358754E-2</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>3.4432102574884196</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5275,13 +5281,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,13 +5300,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5364,7 +5370,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5397,7 +5403,7 @@
         <f>Scenarios!C83</f>
         <v>0.76678821707017375</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5406,11 +5412,11 @@
       <c r="B145" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5433,7 +5439,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5466,7 +5472,7 @@
         <f>Scenarios!C93</f>
         <v>1.1661640402286717</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5475,11 +5481,11 @@
       <c r="B153" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5535,7 +5541,7 @@
         <f>Scenarios!C99</f>
         <v>1.6702761167953912</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5544,11 +5550,11 @@
       <c r="B161" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5604,7 +5610,7 @@
         <f>Scenarios!C105</f>
         <v>1.5081117949794698</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5613,11 +5619,11 @@
       <c r="B169" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5656,13 +5662,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5699,22 +5705,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,6 +5744,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5754,17 +5771,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8114,11 +8120,11 @@
         <f t="shared" si="40"/>
         <v>152761</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8148,11 +8154,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9376,7 +9382,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>6</v>
       </c>
@@ -11447,104 +11453,104 @@
         <v>6970.1947987154417</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>6970.1947987154417</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>12407.845461936662</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="324" t="str">
+      <c r="N48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="324" t="str">
+      <c r="O48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="324" t="str">
+      <c r="P48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>70887</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>70887</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>126188</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="320" t="str">
+      <c r="N49" s="319" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="320" t="str">
+      <c r="O49" s="319" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="320" t="str">
+      <c r="P49" s="319" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13908,47 +13914,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>-0.85134784164611066</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.7312981335354547</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>-85.089361702127661</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>5.6289616404015405E-2</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>-2.9349096133795118</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>-0.18653220872220588</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>0.70290185456337462</v>
       </c>
-      <c r="N113" s="329" t="str">
+      <c r="N113" s="328" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="329" t="str">
+      <c r="O113" s="328" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="329" t="str">
+      <c r="P113" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13960,47 +13966,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>-10.58277261787565</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6195290512667515</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>-41.491956536290409</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-8.9418785233011722</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>14.244552830086286</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>4.5961831887226436</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>49.081843838193791</v>
       </c>
-      <c r="N114" s="329" t="str">
+      <c r="N114" s="328" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="329" t="str">
+      <c r="O114" s="328" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="329" t="str">
+      <c r="P114" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15294,10 +15300,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15312,8 +15318,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15328,8 +15334,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15344,8 +15350,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16839,11 +16845,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 聯易融科技(9959.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16864,8 +16870,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16886,8 +16892,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16897,8 +16903,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -16911,8 +16917,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -16930,8 +16936,8 @@
         <v>-4.8760226650597205E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -16948,8 +16954,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.53605739463275559</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -16966,8 +16972,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9367231569408296</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16993,21 +16999,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17021,8 +17027,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17036,8 +17042,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17057,8 +17063,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17068,8 +17074,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17083,8 +17089,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17094,8 +17100,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17115,8 +17121,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17126,8 +17132,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17141,8 +17147,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17152,8 +17158,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17173,8 +17179,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17184,8 +17190,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17199,8 +17205,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17211,8 +17217,8 @@
         <v>0.3</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17274,8 +17280,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17285,8 +17291,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17300,8 +17306,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17311,8 +17317,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17332,8 +17338,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17343,8 +17349,8 @@
         <v>0.15</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17358,8 +17364,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17369,8 +17375,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17387,7 +17393,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17501,7 +17507,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>0.93217113825685383</v>
       </c>
@@ -17594,7 +17600,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.63556851311953344</v>
       </c>
@@ -17683,7 +17689,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.44575713910823733</v>
       </c>
@@ -17693,7 +17699,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17704,7 +17710,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17716,7 +17722,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17728,7 +17734,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17744,7 +17750,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>0.20616775897983042</v>
       </c>
@@ -17800,7 +17806,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.28199835524143158</v>
       </c>
@@ -17809,32 +17815,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB926A8-63C5-4318-BD12-EC32ADAE1DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A64163A-08E7-4B9C-9106-BC55F5EC25DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4909,7 +4909,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.11984570305671145</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4963,7 +4963,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>115864</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5034,7 +5034,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>4573651.4963457817</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5065,7 +5065,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>23866.7</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5100,7 +5100,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>2.0811961100337415</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5159,111 +5159,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.15</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>2.25 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.08</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>2.12 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.26999999999999996</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.04</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>2.1 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>2.08 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>-0.15</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>2.03 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-115864</v>
       </c>
       <c r="D86" s="248">
@@ -9502,7 +9502,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>4573651.4963457817</v>
       </c>
       <c r="D87" s="248">
@@ -9519,7 +9519,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>23866.7</v>
       </c>
       <c r="D88" s="248">
@@ -15479,7 +15479,7 @@
         <v>22927.986150984863</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15501,7 +15501,7 @@
         <v>23995.854145736514</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15523,7 +15523,7 @@
         <v>25113.457954471374</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15545,7 +15545,7 @@
         <v>26283.11401630432</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15567,7 +15567,7 @@
         <v>27507.246658202934</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15589,7 +15589,7 @@
         <v>28788.393119850305</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15611,7 +15611,7 @@
         <v>30129.208812540193</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15633,7 +15633,7 @@
         <v>31532.472823004497</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15655,7 +15655,7 @@
         <v>33001.093673580872</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15677,7 +15677,7 @@
         <v>34538.115350659325</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15699,7 +15699,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15721,7 +15721,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15743,7 +15743,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15765,7 +15765,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15787,7 +15787,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15809,7 +15809,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15831,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15853,7 +15853,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15875,7 +15875,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -15897,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -15919,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -15941,7 +15941,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -15963,7 +15963,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -15985,7 +15985,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16007,7 +16007,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16029,7 +16029,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16051,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16073,7 +16073,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16095,7 +16095,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16818,7 +16818,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17035,7 +17035,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>2.0811961100337415</v>
       </c>
       <c r="D22" t="str">
@@ -17082,7 +17082,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>2.0974461134820221</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17140,7 +17140,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>2.0811961100337415</v>
       </c>
       <c r="D33" t="str">
@@ -17198,7 +17198,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>2.1171796585916631</v>
       </c>
       <c r="D39" t="str">
@@ -17299,7 +17299,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>2.0279206255855997</v>
       </c>
       <c r="D51" t="str">
@@ -17357,7 +17357,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>2.2513255533708758</v>
       </c>
       <c r="D57" t="str">
@@ -17445,7 +17445,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>2.1004294432871107</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A64163A-08E7-4B9C-9106-BC55F5EC25DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ABEA8E-B801-4E73-964D-CA1E37AAFE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ABEA8E-B801-4E73-964D-CA1E37AAFE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBCC9AA-27E8-4C29-AC8A-84E2C1C4C4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2407,28 +2402,58 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>聯易融科技</t>
+  </si>
+  <si>
+    <t>9959.HK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FIN_03</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>聯易融科技</t>
-  </si>
-  <si>
-    <t>9959.HK</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>FIN_03</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2444,7 +2469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2463,6 +2488,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3111,7 +3137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3617,9 +3643,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3836,29 +3859,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3877,7 +3907,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3924,8 +3968,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4166,15 +4210,15 @@
         <v>45786</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>444</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4189,7 +4233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4198,10 +4242,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>445</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,9 +4259,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4238,20 +4282,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4267,17 +4311,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4291,7 +4335,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4318,73 +4362,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>448</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>442</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>449</v>
+        <v>435</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>449</v>
+        <v>436</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4394,14 +4442,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>2.1040668676405563</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.22664312414291476</v>
       </c>
@@ -4412,96 +4460,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>434</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>9959.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>430</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C29" s="345">
+        <v>426</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>0.76678821707017375</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>427</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>425</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C30" s="346">
+        <v>427</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>1.1661640402286717</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C31" s="346">
+        <v>428</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>1.6702761167953912</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>437</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C32" s="346">
+        <v>429</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>1.5081117949794698</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4510,8 +4558,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4520,22 +4568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4547,13 +4595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4573,13 +4621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4608,13 +4656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4630,19 +4678,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>6970.1947987154417</v>
       </c>
@@ -4650,14 +4698,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-11410</v>
       </c>
@@ -4665,8 +4713,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4700,13 +4748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4722,13 +4770,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4744,22 +4792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4788,26 +4836,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.4102247759095753E-3</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>0</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4820,22 +4876,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4844,7 +4900,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4853,7 +4909,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4864,7 +4920,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4873,42 +4929,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.11984570305671145</v>
       </c>
@@ -4918,8 +4974,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4931,13 +4987,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4950,13 +5006,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4973,9 +5029,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>5.0706701944848852E-2</v>
       </c>
@@ -4985,28 +5041,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>9.7057481271370302E-2</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>1.4790654865358754E-2</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>3.4432102574884196</v>
       </c>
@@ -5044,9 +5100,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.0016120902507897</v>
       </c>
@@ -5075,9 +5131,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.0445018671089587E-2</v>
       </c>
@@ -5087,20 +5143,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>450</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>2.0811961100337415</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5109,10 +5165,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>2.0258239687205015</v>
       </c>
@@ -5122,8 +5178,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5132,49 +5188,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.15</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>2.25 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5192,11 +5248,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>2.12 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.26999999999999996</v>
       </c>
@@ -5214,11 +5270,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>2.1 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
@@ -5236,11 +5292,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>2.08 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5258,11 +5314,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>2.03 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5300,22 +5356,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5326,7 +5382,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5335,7 +5391,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5355,22 +5411,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>9959.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5403,20 +5459,20 @@
         <f>Scenarios!C83</f>
         <v>0.76678821707017375</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5432,14 +5488,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5472,20 +5528,20 @@
         <f>Scenarios!C93</f>
         <v>1.1661640402286717</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5501,12 +5557,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5535,26 +5591,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>1.6702761167953912</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5570,12 +5626,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5604,26 +5660,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>1.5081117949794698</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5638,8 +5694,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5648,113 +5704,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5771,6 +5816,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5783,7 +5839,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6273,7 +6329,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>711319</v>
@@ -6303,7 +6359,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-12356</v>
@@ -6333,7 +6389,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-486204</v>
@@ -6397,7 +6453,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7672,7 +7728,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8120,11 +8176,11 @@
         <f t="shared" si="40"/>
         <v>152761</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8154,11 +8210,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8261,17 +8317,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8355,7 +8411,7 @@
       <c r="C4" s="19">
         <v>218642</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8365,7 +8421,7 @@
       <c r="G4" s="19">
         <v>4898385</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8377,7 +8433,7 @@
         <f>171505+458442+21655</f>
         <v>651602</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8387,7 +8443,7 @@
       <c r="G5" s="19">
         <v>174028</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8398,7 +8454,7 @@
       <c r="C6" s="19">
         <v>0</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8408,7 +8464,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8419,7 +8475,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8429,7 +8485,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8440,7 +8496,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8450,7 +8506,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8461,7 +8517,7 @@
       <c r="C9" s="19">
         <v>1813746</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8471,7 +8527,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8482,10 +8538,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8494,10 +8550,10 @@
       <c r="C11" s="19">
         <v>24965</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8555,7 +8611,7 @@
       <c r="C15" s="19">
         <v>4743</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8564,7 +8620,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8575,7 +8631,7 @@
       <c r="C16" s="19">
         <v>102771</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8584,7 +8640,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8595,7 +8651,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8604,7 +8660,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8615,7 +8671,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8624,7 +8680,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8636,7 +8692,7 @@
         <f>28675+74147</f>
         <v>102822</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8645,7 +8701,7 @@
       <c r="G19" s="19">
         <v>238667</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8656,7 +8712,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8665,7 +8721,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8676,7 +8732,7 @@
       <c r="C21" s="19">
         <v>276368</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8685,7 +8741,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8696,10 +8752,10 @@
       <c r="C22" s="19">
         <v>58201</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8709,10 +8765,10 @@
         <f>28964</f>
         <v>28964</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9045,13 +9101,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9067,7 +9123,7 @@
         <f>H29</f>
         <v>4628975.25</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9082,23 +9138,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>2.0258239687205015</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9112,7 +9168,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.9539978841756818</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9123,22 +9179,22 @@
         <f>G29/G32</f>
         <v>0.91158954067906739</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9152,7 +9208,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>8.9261562605853981E-3</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9166,22 +9222,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9203,22 +9259,22 @@
         <f>G39/G32</f>
         <v>1.1964527413850562E-2</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9232,7 +9288,7 @@
         <f>G28/G29</f>
         <v>-6.6121078416918412E-5</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9251,13 +9307,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9285,7 +9341,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9295,7 +9351,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9305,7 +9361,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9315,26 +9371,26 @@
         <f>SUM(C66:C69)</f>
         <v>5072413</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9345,65 +9401,65 @@
         <v>-83126.91727570309</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>60.75534350764071</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>61.020102347553312</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>498761.50365421851</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>6</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9417,7 +9473,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9431,7 +9487,7 @@
         <f>G19*H19</f>
         <v>23866.7</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9445,7 +9501,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9459,11 +9515,11 @@
         <f>SUM(D79:D81)</f>
         <v>23866.7</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9474,76 +9530,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-115864</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-5.0706701944848852E-2</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>4573651.4963457817</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>2.0016120902507897</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>23866.7</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.0445018671089587E-2</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>4481654.1963457819</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>1.9613504069770304</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9664,7 +9720,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9678,7 +9734,7 @@
         <v>1031173</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9734,7 +9790,7 @@
         <f>C25</f>
         <v>-448336.00730843702</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-462912</v>
@@ -9789,7 +9845,7 @@
         <f>C4+C5</f>
         <v>582836.99269156298</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>568261</v>
@@ -9844,7 +9900,7 @@
         <f>C35</f>
         <v>-549187</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-538958</v>
@@ -9900,7 +9956,7 @@
         <v>33649.992691562977</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9956,7 +10012,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -10011,7 +10067,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -10067,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10123,7 +10179,7 @@
         <f>C50</f>
         <v>-4439.8052012845583</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-4439.8052012845583</v>
@@ -10178,7 +10234,7 @@
         <f>SUM(C8:C12)</f>
         <v>29210.187490278418</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>24863.194798715442</v>
@@ -10233,7 +10289,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-7302.5468725696046</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-92078</v>
@@ -10289,7 +10345,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10346,7 +10402,7 @@
         <v>21907.640617708814</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10403,8 +10459,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10428,8 +10484,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10454,7 +10510,7 @@
         <v>21907.640617708814</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10550,7 +10606,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10574,7 +10630,7 @@
         <v>-295465.98495177622</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10631,7 +10687,7 @@
         <v>-152870.0223566608</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10688,7 +10744,7 @@
         <v>-448336.00730843702</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10737,14 +10793,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10756,8 +10812,8 @@
         <v>0.28653386478483844</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10816,8 +10872,8 @@
         <v>0.14824866667054007</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10874,7 +10930,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.43478253145537848</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.44891788283828221</v>
@@ -10922,14 +10978,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10940,8 +10996,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-217895.5</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10998,8 +11054,8 @@
         <v>-331291.5</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11057,7 +11113,7 @@
         <v>-549187</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11106,14 +11162,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11126,7 +11182,7 @@
         <v>0.21130838375325964</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11184,7 +11240,7 @@
         <v>0.32127635227066653</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11240,7 +11296,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.5325847360239262</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.52266496504466275</v>
@@ -11288,26 +11344,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11386,7 +11442,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11397,7 +11453,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-11410</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-11410</v>
@@ -11446,111 +11502,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>6970.1947987154417</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>6970.1947987154417</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>12407.845461936662</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="323" t="str">
+      <c r="N48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="323" t="str">
+      <c r="O48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="323" t="str">
+      <c r="P48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>70887</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>70887</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>126188</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="319" t="str">
+      <c r="N49" s="318" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="319" t="str">
+      <c r="O49" s="318" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="319" t="str">
+      <c r="P49" s="318" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11564,7 +11620,7 @@
         <f>C47+C48</f>
         <v>-4439.8052012845583</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-4439.8052012845583</v>
@@ -11612,14 +11668,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11633,8 +11689,8 @@
         <f>G53</f>
         <v>1.3975005584127318E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11660,8 +11716,8 @@
         <f>G54</f>
         <v>9.8477525374577088E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11687,7 +11743,7 @@
         <f>-C8/C47</f>
         <v>2.9491667564910586</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>2.5681858019281334</v>
@@ -11735,14 +11791,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11756,7 +11812,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11811,7 +11867,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11866,7 +11922,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11921,7 +11977,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11972,11 +12028,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12032,7 +12088,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-832223</v>
@@ -12080,14 +12136,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12101,7 +12157,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12126,7 +12182,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12151,7 +12207,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12177,7 +12233,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12205,7 +12261,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12227,7 +12283,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12251,7 +12307,7 @@
         <v>0.43478253145537848</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12308,7 +12364,7 @@
         <v>0.56521746854462152</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12365,7 +12421,7 @@
         <v>0.5325847360239262</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12422,7 +12478,7 @@
         <v>3.2632732520695339E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12479,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12536,8 +12592,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>452</v>
+      <c r="E78" s="295" t="s">
+        <v>460</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12595,7 +12651,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12652,7 +12708,7 @@
         <v>4.3055871335697877E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12709,7 +12765,7 @@
         <v>2.8327145387125552E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12766,7 +12822,7 @@
         <v>7.081786346781388E-3</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12819,12 +12875,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12881,7 +12937,7 @@
         <v>2.1245359040344164E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12933,26 +12989,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12962,7 +13018,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12988,7 +13044,7 @@
         <v>2.1245359040344164E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13037,14 +13093,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13056,7 +13112,7 @@
         <f>G90</f>
         <v>0</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0</v>
@@ -13112,7 +13168,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>0</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>0</v>
@@ -13167,7 +13223,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0</v>
@@ -13216,13 +13272,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>0</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>0</v>
@@ -13270,7 +13326,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13279,7 +13335,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13303,7 +13359,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13360,7 +13416,7 @@
         <v>0.17483644908688745</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13438,7 +13494,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13453,7 +13509,7 @@
         <v>8593904</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13510,7 +13566,7 @@
         <v>218642</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13567,7 +13623,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13624,7 +13680,7 @@
         <v>760309</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13681,7 +13737,7 @@
         <v>7833595</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13730,7 +13786,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13739,7 +13795,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13765,7 +13821,7 @@
         <v>0.2120323165947906</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13822,7 +13878,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13879,7 +13935,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13898,63 +13954,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>-0.85134784164611066</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.7312981335354547</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>-85.089361702127661</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>5.6289616404015405E-2</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>-2.9349096133795118</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>-0.18653220872220588</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>0.70290185456337462</v>
       </c>
-      <c r="N113" s="328" t="str">
+      <c r="N113" s="327" t="str">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v/>
       </c>
-      <c r="O113" s="328" t="str">
+      <c r="O113" s="327" t="str">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v/>
       </c>
-      <c r="P113" s="328" t="str">
+      <c r="P113" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13962,58 +14018,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>-10.58277261787565</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6195290512667515</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>-41.491956536290409</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-8.9418785233011722</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>14.244552830086286</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>4.5961831887226436</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>49.081843838193791</v>
       </c>
-      <c r="N114" s="328" t="str">
+      <c r="N114" s="327" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="328" t="str">
+      <c r="O114" s="327" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="328" t="str">
+      <c r="P114" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14022,7 +14078,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14078,7 +14134,7 @@
         <f>C81</f>
         <v>2.8327145387125552E-2</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>2.4111564983485257E-2</v>
@@ -14132,7 +14188,7 @@
         <f>C4/C101</f>
         <v>0.11998888979909481</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.11998888979909481</v>
@@ -14187,7 +14243,7 @@
         <v>1.0970574812713703</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14244,7 +14300,7 @@
         <v>4.2956002565313857E-3</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14340,7 +14396,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14365,7 +14421,7 @@
         <v>9.587656244536915E-3</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14422,7 +14478,7 @@
         <v>8.4102247759095753E-3</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14471,7 +14527,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15204,7 +15260,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15272,7 +15328,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15282,7 +15338,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15300,10 +15356,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15318,8 +15374,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15334,8 +15390,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15350,8 +15406,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16696,7 +16752,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16727,12 +16783,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16747,6 +16803,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>0</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>0</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>446</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>0</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>-0.15</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.04</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.08</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.15</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>0</v>
+      </c>
+      <c r="C51" s="124">
+        <v>0</v>
+      </c>
+      <c r="D51" s="124">
+        <v>0</v>
+      </c>
+      <c r="E51" s="124">
+        <v>0</v>
+      </c>
+      <c r="F51" s="124">
+        <v>0</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>0</v>
+      </c>
+      <c r="C52" s="124">
+        <v>0</v>
+      </c>
+      <c r="D52" s="124">
+        <v>0</v>
+      </c>
+      <c r="E52" s="124">
+        <v>0</v>
+      </c>
+      <c r="F52" s="124">
+        <v>0</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>0</v>
+      </c>
+      <c r="C53" s="124">
+        <v>0</v>
+      </c>
+      <c r="D53" s="124">
+        <v>0</v>
+      </c>
+      <c r="E53" s="124">
+        <v>0</v>
+      </c>
+      <c r="F53" s="124">
+        <v>0</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>0</v>
+      </c>
+      <c r="C54" s="124">
+        <v>0</v>
+      </c>
+      <c r="D54" s="124">
+        <v>0</v>
+      </c>
+      <c r="E54" s="124">
+        <v>0</v>
+      </c>
+      <c r="F54" s="124">
+        <v>0</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>0</v>
+      </c>
+      <c r="C55" s="124">
+        <v>0</v>
+      </c>
+      <c r="D55" s="124">
+        <v>0</v>
+      </c>
+      <c r="E55" s="124">
+        <v>0</v>
+      </c>
+      <c r="F55" s="124">
+        <v>0</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>0</v>
+      </c>
+      <c r="C56" s="124">
+        <v>0</v>
+      </c>
+      <c r="D56" s="124">
+        <v>0</v>
+      </c>
+      <c r="E56" s="124">
+        <v>0</v>
+      </c>
+      <c r="F56" s="124">
+        <v>0</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>-0.15</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.04</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.08</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.15</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.15</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.08</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.26999999999999996</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.04</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>-0.15</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16767,19 +18274,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-1.1399999999999999</v>
       </c>
@@ -16796,19 +18303,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -16822,13 +18329,13 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>2.1040668676405563</v>
       </c>
@@ -16845,15 +18352,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 聯易融科技(9959.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16870,12 +18377,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16892,37 +18399,37 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>448</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16936,12 +18443,12 @@
         <v>-4.8760226650597205E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16954,12 +18461,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.53605739463275559</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16972,8 +18479,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9367231569408296</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16989,7 +18496,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16999,25 +18506,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17027,23 +18534,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>2.0811961100337415</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17063,8 +18570,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17074,23 +18581,23 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>2.0974461134820221</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17100,8 +18607,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17121,8 +18628,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17132,23 +18639,23 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>2.0811961100337415</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17158,8 +18665,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17179,8 +18686,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17190,23 +18697,23 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>2.1171796585916631</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17217,8 +18724,8 @@
         <v>0.3</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17280,8 +18787,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17291,23 +18798,23 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>2.0279206255855997</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17317,12 +18824,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17338,8 +18845,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17349,23 +18856,23 @@
         <v>0.15</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>2.2513255533708758</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17375,8 +18882,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17391,16 +18898,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17409,10 +18916,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17424,8 +18931,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17436,8 +18943,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17445,30 +18952,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>2.1004294432871107</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17476,38 +18983,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>0.93217113825685383</v>
       </c>
@@ -17527,10 +19034,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17551,12 +19058,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17600,7 +19107,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.63556851311953344</v>
       </c>
@@ -17610,14 +19117,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>1.1399999999999999</v>
       </c>
@@ -17628,9 +19135,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.22664312414291476</v>
       </c>
@@ -17640,12 +19147,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17689,28 +19196,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.44575713910823733</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17722,7 +19229,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17734,23 +19241,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>1.6702761167953912</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>0.20616775897983042</v>
       </c>
@@ -17760,12 +19267,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17794,19 +19301,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>1.5081117949794698</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.28199835524143158</v>
       </c>
@@ -17815,33 +19322,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CD7FDD-3A56-184C-B112-FAC882818D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356F9F4F-D25C-4347-B595-8608A13CE40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5100" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3874,6 +3874,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3909,9 +3912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4220,7 +4220,7 @@
       <c r="C1" s="44">
         <v>45786</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>461</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4375,13 +4375,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4581,22 +4581,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4608,13 +4608,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4634,13 +4634,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4669,13 +4669,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4691,13 +4691,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4783,13 +4783,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4805,22 +4805,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4889,22 +4889,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4948,22 +4948,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -5000,13 +5000,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5019,13 +5019,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5156,13 +5156,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5201,13 +5201,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5350,13 +5350,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5369,22 +5369,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5717,13 +5717,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5731,13 +5731,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5760,13 +5760,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15369,10 +15369,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15387,8 +15387,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15403,8 +15403,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15419,8 +15419,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -16899,8 +16899,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18365,11 +18365,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 聯易融科技(9959.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18390,8 +18390,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18412,8 +18412,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18423,8 +18423,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18437,8 +18437,8 @@
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18456,8 +18456,8 @@
         <v>-4.8760226650597205E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18474,8 +18474,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.53605739463275559</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18492,8 +18492,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9367231569408296</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18519,21 +18519,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18547,8 +18547,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18562,8 +18562,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18583,8 +18583,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18594,8 +18594,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18609,8 +18609,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18620,8 +18620,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18641,8 +18641,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18652,8 +18652,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18667,8 +18667,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18678,8 +18678,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18699,8 +18699,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18710,8 +18710,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18725,8 +18725,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18737,8 +18737,8 @@
         <v>0.3</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18800,8 +18800,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18811,8 +18811,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18826,8 +18826,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18837,8 +18837,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18858,8 +18858,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18869,8 +18869,8 @@
         <v>0.15</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18884,8 +18884,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -18895,8 +18895,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356F9F4F-D25C-4347-B595-8608A13CE40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A0E0EC-6846-458C-BB06-E9D71AA0B2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5100" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2491,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3915,7 +3904,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4204,7 +4193,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4213,7 +4202,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4230,7 +4219,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4244,7 +4233,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>416</v>
       </c>
@@ -4253,7 +4242,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4261,7 +4250,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4270,7 +4259,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4280,7 +4269,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4290,17 +4279,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>418</v>
       </c>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4322,7 +4311,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>417</v>
       </c>
@@ -4332,7 +4321,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>421</v>
       </c>
@@ -4346,7 +4335,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>420</v>
       </c>
@@ -4360,7 +4349,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4370,11 +4359,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4383,14 +4372,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4405,7 +4394,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4418,7 +4407,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>435</v>
       </c>
@@ -4426,7 +4415,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>436</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4450,28 +4439,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>2.1040668676405563</v>
+        <v>2.1131011468081908</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22664312414291476</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.22839623911312068</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>434</v>
       </c>
@@ -4490,13 +4479,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>0.76678821707017375</v>
+        <v>0.82648230361166808</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,16 +4495,16 @@
         <v>425</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>1.1661640402286717</v>
+        <v>1.1711712249606363</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4528,13 +4517,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>1.6702761167953912</v>
+        <v>1.7009631025661165</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4544,16 +4533,16 @@
         <v>437</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>1.5081117949794698</v>
+        <v>1.514587208466269</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4566,11 +4555,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4580,7 +4569,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4589,7 +4578,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4598,7 +4587,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4607,7 +4596,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4616,7 +4605,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4629,11 +4618,11 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4642,7 +4631,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4655,7 +4644,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4668,7 +4657,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4677,7 +4666,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4690,7 +4679,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4699,7 +4688,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4714,7 +4703,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4729,7 +4718,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4742,12 +4731,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4760,7 +4749,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4769,7 +4758,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4782,7 +4771,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4791,7 +4780,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4804,7 +4793,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4813,7 +4802,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4822,7 +4811,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4835,7 +4824,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4848,7 +4837,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4858,7 +4847,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4874,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4884,10 +4873,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4897,7 +4886,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4906,21 +4895,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>431</v>
       </c>
@@ -4929,25 +4918,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4956,7 +4945,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4965,7 +4954,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4973,20 +4962,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11984570305671145</v>
+        <v>0.12783541659382552</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4996,10 +4985,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5008,17 +4997,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5027,7 +5016,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5040,7 +5029,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5053,7 +5042,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5062,7 +5051,7 @@
         <v>9.7057481271370302E-2</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5071,7 +5060,7 @@
         <v>1.4790654865358754E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5080,12 +5069,12 @@
         <v>3.4432102574884196</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5098,7 +5087,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5111,7 +5100,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5124,12 +5113,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5142,7 +5131,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5155,7 +5144,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5164,20 +5153,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>450</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5190,7 +5179,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5200,7 +5189,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5209,7 +5198,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5226,7 +5215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5241,14 +5230,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>2.25 HKD</v>
+        <v>2.27 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5263,14 +5252,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>2.12 HKD</v>
+        <v>2.13 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5285,14 +5274,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>2.1 HKD</v>
+        <v>2.11 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5307,14 +5296,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>2.08 HKD</v>
+        <v>2.09 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5336,20 +5325,20 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>2.1040668676405563</v>
+        <v>2.1131011468081908</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5358,7 +5347,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5368,7 +5357,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5377,7 +5366,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5386,12 +5375,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5400,16 +5389,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5422,7 +5411,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5435,16 +5424,16 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5454,30 +5443,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>0.76678821707017375</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.82648230361166808</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>0.76678821707017375</v>
+        <v>0.82648230361166808</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>417</v>
       </c>
@@ -5490,21 +5479,21 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.63556851311953344</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.60887707393464918</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5513,7 +5502,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5523,30 +5512,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>1.1661640402286717</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>1.1711712249606363</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>1.1661640402286717</v>
+        <v>1.1711712249606363</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>417</v>
       </c>
@@ -5559,7 +5548,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
@@ -5568,21 +5557,21 @@
         <v>0.44575713910823733</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5592,30 +5581,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>1.6702761167953912</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>1.7009631025661165</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>1.6702761167953912</v>
+        <v>1.7009631025661165</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>417</v>
       </c>
@@ -5628,21 +5617,21 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.20616775897983042</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.19503943049039696</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>424</v>
       </c>
@@ -5651,7 +5640,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5661,30 +5650,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>1.5081117949794698</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>1.514587208466269</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>1.5081117949794698</v>
+        <v>1.514587208466269</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>417</v>
       </c>
@@ -5697,16 +5686,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.28199835524143158</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.2819299041708756</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5716,7 +5705,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5725,12 +5714,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5739,27 +5728,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5768,12 +5757,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5782,7 +5771,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5791,22 +5780,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5867,15 +5856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -5924,7 +5913,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5940,7 +5929,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5948,7 +5937,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5978,7 +5967,7 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6008,7 +5997,7 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6038,7 +6027,7 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6068,7 +6057,7 @@
       <c r="L7" s="188"/>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6098,7 +6087,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6114,7 +6103,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6130,7 +6119,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6146,7 +6135,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6176,7 +6165,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6196,7 +6185,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6226,7 +6215,7 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6256,7 +6245,7 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6286,13 +6275,13 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6308,7 +6297,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6324,7 +6313,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6340,7 +6329,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6370,7 +6359,7 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6400,7 +6389,7 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6430,7 +6419,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6461,7 +6450,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6469,7 +6458,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6500,7 +6489,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6531,7 +6520,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6562,7 +6551,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6593,7 +6582,7 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6624,7 +6613,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6640,12 +6629,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6694,7 +6683,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6743,7 +6732,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6792,7 +6781,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6841,7 +6830,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6890,7 +6879,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -6939,7 +6928,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -6988,7 +6977,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7037,7 +7026,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7086,7 +7075,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7135,7 +7124,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7184,7 +7173,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7233,7 +7222,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7282,12 +7271,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7336,7 +7325,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7385,12 +7374,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7439,7 +7428,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7488,7 +7477,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7537,7 +7526,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7586,13 +7575,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7641,7 +7630,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7690,7 +7679,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7739,7 +7728,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7788,7 +7777,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7837,12 +7826,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7892,7 +7881,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -7941,7 +7930,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7991,7 +7980,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8040,7 +8029,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8090,7 +8079,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8106,13 +8095,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8161,7 +8150,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8195,7 +8184,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8229,7 +8218,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8278,7 +8267,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8359,7 +8348,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8370,7 +8359,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8386,7 +8375,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8397,7 +8386,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8417,7 +8406,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8438,7 +8427,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8460,7 +8449,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8481,7 +8470,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8502,7 +8491,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8523,7 +8512,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8544,7 +8533,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8556,7 +8545,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8568,7 +8557,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8592,12 +8581,12 @@
         <v>4530366.0999999996</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8617,7 +8606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8637,7 +8626,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8657,7 +8646,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8677,7 +8666,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8697,7 +8686,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8718,7 +8707,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8738,7 +8727,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8758,7 +8747,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8770,7 +8759,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8783,7 +8772,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8807,7 +8796,7 @@
         <v>23866.7</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8824,7 +8813,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8843,7 +8832,7 @@
         <v>4628457.25</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8858,7 +8847,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8877,7 +8866,7 @@
         <v>4628975.25</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8893,7 +8882,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8910,7 +8899,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8930,7 +8919,7 @@
         <v>5388766.25</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8941,7 +8930,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -8954,7 +8943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -8973,7 +8962,7 @@
         <v>834533.45</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8989,7 +8978,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9005,7 +8994,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9021,7 +9010,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9040,7 +9029,7 @@
         <v>10282.200000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9060,7 +9049,7 @@
         <v>4554232.8</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9080,7 +9069,7 @@
         <v>4530366.0999999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9099,7 +9088,7 @@
         <v>23866.7</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9110,7 +9099,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9124,7 +9113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9138,7 +9127,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9153,10 +9142,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9169,7 +9158,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9183,7 +9172,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9194,10 +9183,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9209,7 +9198,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9223,7 +9212,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9237,10 +9226,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9252,7 +9241,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9263,7 +9252,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9274,10 +9263,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9289,7 +9278,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9305,7 +9294,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9316,7 +9305,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9330,7 +9319,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9346,7 +9335,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9356,7 +9345,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9366,7 +9355,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9376,7 +9365,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9386,10 +9375,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9401,7 +9390,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9417,7 +9406,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9433,7 +9422,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9446,7 +9435,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9459,10 +9448,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9474,7 +9463,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9488,7 +9477,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9502,7 +9491,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9516,7 +9505,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9530,7 +9519,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9541,7 +9530,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9549,7 +9538,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9566,7 +9555,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9583,7 +9572,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9600,7 +9589,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9631,19 +9620,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9700,7 +9689,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9723,7 +9712,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9737,7 +9726,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9794,7 +9783,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9849,7 +9838,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9904,7 +9893,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -9959,7 +9948,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10016,7 +10005,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10071,7 +10060,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10126,7 +10115,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10183,7 +10172,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10238,7 +10227,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10293,7 +10282,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10348,7 +10337,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10405,7 +10394,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10462,7 +10451,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10488,7 +10477,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10513,7 +10502,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10570,7 +10559,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10589,7 +10578,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10612,7 +10601,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10633,7 +10622,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10690,7 +10679,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10747,7 +10736,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10804,18 +10793,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10874,7 +10863,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10934,7 +10923,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -10989,18 +10978,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11057,7 +11046,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11116,7 +11105,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11173,18 +11162,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11242,7 +11231,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11300,7 +11289,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11355,18 +11344,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11424,10 +11413,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11450,14 +11439,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11512,7 +11501,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11567,7 +11556,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11624,7 +11613,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11679,11 +11668,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11693,7 +11682,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11720,7 +11709,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11747,7 +11736,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11802,11 +11791,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11816,7 +11805,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11871,7 +11860,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11926,7 +11915,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -11981,7 +11970,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12036,7 +12025,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12092,7 +12081,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12147,11 +12136,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12161,7 +12150,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12186,7 +12175,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12211,7 +12200,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12236,7 +12225,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12263,10 +12252,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12289,7 +12278,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12310,7 +12299,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12367,7 +12356,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12424,7 +12413,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12481,7 +12470,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12538,7 +12527,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12595,7 +12584,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12654,7 +12643,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12711,7 +12700,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12768,7 +12757,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12825,7 +12814,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12882,7 +12871,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12940,7 +12929,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -12997,7 +12986,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13023,7 +13012,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13047,7 +13036,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13104,18 +13093,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13171,7 +13160,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13227,7 +13216,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13282,7 +13271,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13337,11 +13326,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13362,7 +13351,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13419,7 +13408,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13476,10 +13465,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13502,7 +13491,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13512,7 +13501,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13569,7 +13558,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13626,7 +13615,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13683,7 +13672,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13740,7 +13729,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13797,11 +13786,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13824,7 +13813,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13881,7 +13870,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -13938,7 +13927,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -13965,18 +13954,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14028,7 +14017,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14080,11 +14069,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14138,7 +14127,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14193,7 +14182,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14247,7 +14236,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14303,7 +14292,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14360,7 +14349,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14379,7 +14368,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14402,7 +14391,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14423,7 +14412,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14481,7 +14470,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14538,7 +14527,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14588,688 +14577,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15291,16 +15280,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15312,7 +15301,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15325,7 +15314,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15346,24 +15335,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>273845.50772136019</v>
+        <v>292101.87490278418</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15375,7 +15364,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15391,7 +15380,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15407,7 +15396,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15423,13 +15412,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>4755499.7040671417</v>
+        <v>4773756.0712485658</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15437,7 +15426,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15451,13 +15440,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15465,10 +15454,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15478,13 +15467,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15494,7 +15483,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15504,13 +15493,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>2.1004294432871107</v>
+        <v>2.1092470181722871</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15518,10 +15507,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15539,7 +15528,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15553,15 +15542,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>21229.616806467464</v>
+        <v>21328.359210218478</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15575,15 +15564,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>20572.577285439398</v>
+        <v>20764.395150448039</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15597,15 +15586,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>19935.872607763817</v>
+        <v>20215.343417386746</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15619,15 +15608,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>19318.873426436563</v>
+        <v>19680.809699581539</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15641,15 +15630,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>18720.969872235772</v>
+        <v>19160.410111955138</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15663,15 +15652,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>18141.570950900201</v>
+        <v>18653.770920112023</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15685,15 +15674,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>17580.103958964446</v>
+        <v>18160.528271934294</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15707,15 +15696,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>17036.013917673507</v>
+        <v>17680.327936274669</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15729,15 +15718,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>16508.76302441736</v>
+        <v>17212.825048559003</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15751,15 +15740,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>15997.83012114307</v>
+        <v>16757.683863115508</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15781,7 +15770,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15803,7 +15792,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15825,7 +15814,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15847,7 +15836,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15869,7 +15858,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15891,7 +15880,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15913,7 +15902,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15935,7 +15924,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15957,7 +15946,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15979,7 +15968,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16001,7 +15990,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16023,7 +16012,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16045,7 +16034,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16067,7 +16056,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16089,7 +16078,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16111,7 +16100,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16133,7 +16122,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16155,7 +16144,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16177,7 +16166,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16199,13 +16188,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>286599.82688731077</v>
+        <v>305706.48201313155</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16213,30 +16202,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>132751.17350040015</v>
+        <v>148326.92891517226</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>317793.36547184177</v>
+        <v>337941.38254475768</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16246,10 +16235,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>317793.36547184177</v>
+        <v>337941.38254475768</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16273,141 +16262,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>214932.39161073393</v>
+        <v>230129.32318596085</v>
       </c>
       <c r="C56" s="124">
-        <v>273845.50772136013</v>
+        <v>292101.87490278418</v>
       </c>
       <c r="D56" s="124">
-        <v>291781.51194251317</v>
+        <v>310897.11030257697</v>
       </c>
       <c r="E56" s="124">
-        <v>310822.82631794544</v>
+        <v>330819.52404469467</v>
       </c>
       <c r="F56" s="124">
-        <v>347100.63095258689</v>
+        <v>368698.25126552512</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>181396.86316805036</v>
+        <v>195323.71296478334</v>
       </c>
       <c r="C57" s="124">
-        <v>273845.50772136007</v>
+        <v>292101.87490278424</v>
       </c>
       <c r="D57" s="124">
-        <v>310976.50475562562</v>
+        <v>330834.80812820001</v>
       </c>
       <c r="E57" s="124">
-        <v>356067.3385682886</v>
+        <v>377823.75842714385</v>
       </c>
       <c r="F57" s="124">
-        <v>460387.76753897907</v>
+        <v>486432.8926548186</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>152111.88093543128</v>
+        <v>164231.2612386971</v>
       </c>
       <c r="C58" s="124">
-        <v>273845.50772136002</v>
+        <v>292101.87490278424</v>
       </c>
       <c r="D58" s="124">
-        <v>335999.61210322619</v>
+        <v>357421.37846912513</v>
       </c>
       <c r="E58" s="124">
-        <v>421848.33599707007</v>
+        <v>447729.73870152939</v>
       </c>
       <c r="F58" s="124">
-        <v>662588.55482888664</v>
+        <v>701400.51267742459</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>130229.85174283449</v>
+        <v>140456.96258364385</v>
       </c>
       <c r="C59" s="124">
-        <v>273845.50772136002</v>
+        <v>292101.87490278424</v>
       </c>
       <c r="D59" s="124">
-        <v>362932.63451683585</v>
+        <v>386702.33222141815</v>
       </c>
       <c r="E59" s="124">
-        <v>501606.12016442942</v>
+        <v>534460.50232245121</v>
       </c>
       <c r="F59" s="124">
-        <v>971451.15939064755</v>
+        <v>1037416.7285353488</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>114748.10150863045</v>
+        <v>123242.60416404021</v>
       </c>
       <c r="C60" s="124">
-        <v>273845.50772136002</v>
+        <v>292101.8749027843</v>
       </c>
       <c r="D60" s="124">
-        <v>389462.57783631247</v>
+        <v>416218.57809877704</v>
       </c>
       <c r="E60" s="124">
-        <v>590876.27053458907</v>
+        <v>633803.56595403072</v>
       </c>
       <c r="F60" s="124">
-        <v>1416078.7444713688</v>
+        <v>1532453.3884392621</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>104033.55410486754</v>
+        <v>111049.61340254245</v>
       </c>
       <c r="C61" s="124">
-        <v>273845.50772135996</v>
+        <v>292101.8749027843</v>
       </c>
       <c r="D61" s="124">
-        <v>414308.10486932099</v>
+        <v>444507.59329352563</v>
       </c>
       <c r="E61" s="124">
-        <v>686620.37750640651</v>
+        <v>742845.64601743023</v>
       </c>
       <c r="F61" s="124">
-        <v>2039582.5990240611</v>
+        <v>2242918.121417555</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16417,7 +16406,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>-0.15</v>
@@ -16440,193 +16429,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.05541338356768</v>
+        <v>2.0620641662082004</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.0890456199774996</v>
+        <v>2.0974113673066199</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>2.097378857675777</v>
+        <v>2.106130209187131</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>2.1132554701423083</v>
+        <v>2.122707449151545</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>2.0407369004037452</v>
+        <v>2.0468318446631666</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>2.0974461134820221</v>
+        <v>2.1061368981109276</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>2.1171796585916631</v>
+        <v>2.1267011346081133</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>2.1628344340057311</v>
+        <v>2.1742328182870017</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>2.0279206255855997</v>
+        <v>2.0332245491925347</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>2.108397222074931</v>
+        <v>2.1177722403916452</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>2.1459680435106723</v>
+        <v>2.1572947763426966</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>2.2513255533708758</v>
+        <v>2.2683112122340416</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>2.0183441779209454</v>
+        <v>2.0228199690308832</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>2.1201841855838794</v>
+        <v>2.1305867521863218</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>2.1808732270841369</v>
+        <v>2.1952516134998397</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>2.3864961329419501</v>
+        <v>2.4153652937964232</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>2.0115687472892536</v>
+        <v>2.0152862800372824</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>2.1317947456242234</v>
+        <v>2.1435042371879973</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>2.2199414010414618</v>
+        <v>2.2387280955637645</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>2.5810828763061187</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>2.6320130563932715</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0068796345219004</v>
+        <v>2.0099501415614864</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>2.1426681379973975</v>
+        <v>2.1558846371551437</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>2.261842836303456</v>
+        <v>2.286449253587147</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>2.8539530008855203</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>2.9429407255351698</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16643,7 +16632,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16658,14 +16647,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>2.2513255533708758</v>
+        <v>2.2683112122340416</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16680,7 +16669,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>2.1171796585916631</v>
+        <v>2.1267011346081133</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16688,7 +16677,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16703,7 +16692,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>2.0974461134820221</v>
+        <v>2.1061368981109276</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16711,7 +16700,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16726,7 +16715,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16734,7 +16723,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16749,21 +16738,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.0279206255855997</v>
+        <v>2.0332245491925347</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16771,23 +16760,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16821,16 +16810,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>444</v>
       </c>
@@ -16842,7 +16831,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>443</v>
       </c>
@@ -16855,7 +16844,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>441</v>
       </c>
@@ -16876,18 +16865,18 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>442</v>
       </c>
@@ -16903,7 +16892,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>445</v>
       </c>
@@ -16917,10 +16906,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -16930,13 +16919,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -16946,7 +16935,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -16956,7 +16945,7 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
@@ -16970,10 +16959,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -16991,7 +16980,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17005,7 +16994,7 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
@@ -17013,7 +17002,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17027,7 +17016,7 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
@@ -17035,7 +17024,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17049,7 +17038,7 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
@@ -17057,7 +17046,7 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17071,7 +17060,7 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
@@ -17079,7 +17068,7 @@
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17093,7 +17082,7 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
@@ -17101,7 +17090,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17115,7 +17104,7 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
@@ -17123,7 +17112,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17137,7 +17126,7 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
@@ -17145,7 +17134,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17159,7 +17148,7 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
@@ -17167,7 +17156,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17181,7 +17170,7 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
@@ -17189,7 +17178,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17203,7 +17192,7 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
@@ -17211,7 +17200,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17233,7 +17222,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17255,7 +17244,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17277,7 +17266,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17299,7 +17288,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17321,7 +17310,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17343,7 +17332,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17365,7 +17354,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17387,7 +17376,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17409,7 +17398,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17431,7 +17420,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17453,7 +17442,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17475,7 +17464,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17497,7 +17486,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17519,7 +17508,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17541,7 +17530,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17563,7 +17552,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17585,7 +17574,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17607,7 +17596,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17629,7 +17618,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17651,7 +17640,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
@@ -17665,7 +17654,7 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
@@ -17673,7 +17662,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
@@ -17684,11 +17673,11 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17698,7 +17687,7 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
         <v>0</v>
@@ -17725,7 +17714,7 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
@@ -17747,7 +17736,7 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
@@ -17768,7 +17757,7 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
@@ -17789,7 +17778,7 @@
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
@@ -17810,7 +17799,7 @@
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
@@ -17831,7 +17820,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
@@ -17852,14 +17841,14 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17869,7 +17858,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>-0.15</v>
@@ -17892,7 +17881,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
@@ -17918,7 +17907,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -17945,7 +17934,7 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -17972,7 +17961,7 @@
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -17999,7 +17988,7 @@
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18026,7 +18015,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18052,7 +18041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18078,7 +18067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18095,7 +18084,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18117,7 +18106,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18140,7 +18129,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18163,7 +18152,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18186,7 +18175,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18208,14 +18197,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18223,23 +18212,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18269,7 +18258,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18279,7 +18268,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18292,7 +18281,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18304,7 +18293,7 @@
         <v>-1.1399999999999999</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18324,7 +18313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18333,7 +18322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18350,10 +18339,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>2.1040668676405563</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2.1131011468081908</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18378,7 +18367,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18400,7 +18389,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18422,7 +18411,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18433,7 +18422,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
@@ -18447,7 +18436,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18466,7 +18455,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18484,7 +18473,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18495,7 +18484,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18504,7 +18493,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18512,7 +18501,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18524,18 +18513,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18550,13 +18539,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18565,7 +18554,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18574,7 +18563,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18586,7 +18575,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18597,13 +18586,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>2.0974461134820221</v>
+        <v>2.1061368981109276</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18612,7 +18601,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18623,7 +18612,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18632,7 +18621,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18644,7 +18633,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18655,13 +18644,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>2.0811961100337415</v>
+        <v>2.089185823570856</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18670,7 +18659,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18681,7 +18670,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18690,7 +18679,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18702,7 +18691,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18713,13 +18702,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>2.1171796585916631</v>
+        <v>2.1267011346081133</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18728,7 +18717,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18740,20 +18729,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>2.1001161763252583</v>
+        <v>2.108915954152069</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18762,12 +18751,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18777,12 +18766,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18791,7 +18780,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18803,7 +18792,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18814,13 +18803,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>2.0279206255855997</v>
+        <v>2.0332245491925347</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18829,7 +18818,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18840,7 +18829,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18849,7 +18838,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18861,7 +18850,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18872,13 +18861,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>2.2513255533708758</v>
+        <v>2.2683112122340416</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18887,7 +18876,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18898,13 +18887,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>2.1040668676405563</v>
+        <v>2.1131011468081908</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -18918,7 +18907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -18927,7 +18916,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -18935,7 +18924,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -18948,7 +18937,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -18960,13 +18949,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>2.1004294432871107</v>
+        <v>2.1092470181722871</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -18976,7 +18965,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -18984,7 +18973,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -18994,7 +18983,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19006,7 +18995,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19016,7 +19005,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19029,10 +19018,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.93217113825685383</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.92818576618522131</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19041,12 +19030,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19056,7 +19045,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19069,21 +19058,21 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
@@ -19095,23 +19084,23 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>0.76678821707017375</v>
+        <v>0.82648230361166808</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>0.76678821707017375</v>
+        <v>0.82648230361166808</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19122,18 +19111,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.63556851311953344</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.60887707393464918</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19146,24 +19135,24 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22664312414291476</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.22839623911312068</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
@@ -19172,7 +19161,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
@@ -19184,23 +19173,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>1.1661640402286717</v>
+        <v>1.1711712249606363</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>1.1661640402286717</v>
+        <v>1.1711712249606363</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19214,25 +19203,25 @@
         <v>0.44575713910823733</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
@@ -19244,25 +19233,25 @@
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>1.6702761167953912</v>
+        <v>1.7009631025661165</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>1.6702761167953912</v>
+        <v>1.7009631025661165</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19272,18 +19261,18 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>0.20616775897983042</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.19503943049039696</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>422</v>
       </c>
@@ -19292,7 +19281,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
@@ -19302,23 +19291,23 @@
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>1.5081117949794698</v>
+        <v>1.514587208466269</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>1.5081117949794698</v>
+        <v>1.514587208466269</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19328,19 +19317,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.28199835524143158</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.2819299041708756</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19348,7 +19337,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19356,7 +19345,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A0E0EC-6846-458C-BB06-E9D71AA0B2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9699F3EB-A176-4D3D-A44F-3594BA1CD146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3866,29 +3866,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4306,7 +4306,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.1399999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2604.8817007199996</v>
+        <v>2719.13089812</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4364,13 +4364,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22839623911312068</v>
+        <v>0.21094506441990801</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4570,22 +4570,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4597,13 +4597,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4623,13 +4623,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4658,13 +4658,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4680,13 +4680,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4750,13 +4750,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4772,7 +4772,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4794,22 +4794,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.4102247759095753E-3</v>
+        <v>8.0568539870058114E-3</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4878,22 +4878,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4937,22 +4937,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4989,13 +4989,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5008,13 +5008,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5190,13 +5190,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5339,13 +5339,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5358,22 +5358,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5706,13 +5706,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5749,13 +5749,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5763,22 +5763,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5802,17 +5802,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5829,6 +5818,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14477,38 +14477,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.4102247759095753E-3</v>
+        <v>8.0568539870058114E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.5803400278295217E-2</v>
+        <v>-2.4719223796013903E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.6844623877827242E-2</v>
+        <v>-7.361585816867483E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.720577175831511E-2</v>
+        <v>-1.648284017183128E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.1393748121995906E-2</v>
+        <v>3.0074683074853222E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.6592205304084868E-2</v>
+        <v>5.4214381551812393E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6857195467979532E-2</v>
+        <v>1.6148909944114848E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.7535190924092508E-3</v>
+        <v>-7.4277409792828115E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14534,31 +14534,31 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.32075199413818239</v>
+        <v>-0.30727501959456127</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.17017970523477924</v>
+        <v>-0.16302929745180531</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.390016327405268E-3</v>
+        <v>-8.0374946329764742E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.9870491225798563</v>
+        <v>-4.7775092434798623</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.27466967110338941</v>
+        <v>-0.26312892862005371</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.41536396823738214</v>
+        <v>-0.39791170066438286</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.54140846381245877</v>
+        <v>-0.51866020903042265</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-1.1399999999999999</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>1.1399999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>1.1399999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22839623911312068</v>
+        <v>0.21094506441990801</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF451E2-6B55-4476-B660-040B0C809BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353597AC-1D4D-42C8-A19B-0CEA97EE3B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3865,29 +3865,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2719.13089812</v>
+        <v>2696.2810586400001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,13 +4363,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21094506441990801</v>
+        <v>0.21435619529683625</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4569,22 +4569,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4596,13 +4596,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4622,13 +4622,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4657,13 +4657,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4749,13 +4749,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4793,22 +4793,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.0568539870058114E-3</v>
+        <v>8.1251324106245051E-3</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4877,22 +4877,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4936,22 +4936,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4988,13 +4988,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5007,13 +5007,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5144,13 +5144,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5189,13 +5189,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5338,13 +5338,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5357,22 +5357,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5705,13 +5705,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5762,22 +5762,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5801,6 +5801,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5817,17 +5828,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14479,38 +14479,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0568539870058114E-3</v>
+        <v>8.1251324106245051E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.4719223796013903E-2</v>
+        <v>-2.492870874343775E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.361585816867483E-2</v>
+        <v>-7.4239721373494119E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.648284017183128E-2</v>
+        <v>-1.662252525803324E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.0074683074853222E-2</v>
+        <v>3.0329553270402824E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4214381551812393E-2</v>
+        <v>5.4673825463268433E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6148909944114848E-2</v>
+        <v>1.6285765113132768E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.4277409792828115E-3</v>
+        <v>-7.4906879367343613E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14536,31 +14536,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30727501959456127</v>
+        <v>-0.30987904518434572</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16302929745180531</v>
+        <v>-0.16441090166749858</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.0374946329764742E-3</v>
+        <v>-8.1056089942728848E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.7775092434798623</v>
+        <v>-4.8179966099500309</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.26312892862005371</v>
+        <v>-0.26535883479479994</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.39791170066438286</v>
+        <v>-0.40128383372086074</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.51866020903042265</v>
+        <v>-0.52305563453068049</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.19</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21094506441990801</v>
+        <v>0.21435619529683625</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D03CB5E-ADC8-4D4B-A625-ED4A5600D4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC0DB37-E18A-4073-A3C7-FC25F5FD811C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3879,29 +3879,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4319,7 +4319,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.18</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2696.2810586400001</v>
+        <v>2650.5813796799998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4377,13 +4377,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21435619529683625</v>
+        <v>0.2212955241882848</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4583,22 +4583,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,13 +4610,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4636,13 +4636,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4671,13 +4671,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4693,13 +4693,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4763,13 +4763,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4785,7 +4785,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4807,22 +4807,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.1251324106245051E-3</v>
+        <v>8.265220900462859E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5016,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5068,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,13 +5087,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5215,13 +5215,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5260,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5409,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5428,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5776,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5819,13 +5819,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5833,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5872,6 +5872,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5888,17 +5899,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14550,38 +14550,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1251324106245051E-3</v>
+        <v>8.265220900462859E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.492870874343775E-2</v>
+        <v>-2.535851406660047E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.4239721373494119E-2</v>
+        <v>-7.5519716569588835E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.662252525803324E-2</v>
+        <v>-1.6909120521102779E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.0329553270402824E-2</v>
+        <v>3.0852476602651148E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4673825463268433E-2</v>
+        <v>5.5616477626428233E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6285765113132768E-2</v>
+        <v>1.6566554166807471E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.4906879367343613E-3</v>
+        <v>-7.6198377287470228E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14607,31 +14607,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30987904518434572</v>
+        <v>-0.31522178734269651</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16441090166749858</v>
+        <v>-0.16724557238590373</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.1056089942728848E-3</v>
+        <v>-8.2453608734844863E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8179966099500309</v>
+        <v>-4.901065517018135</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.26535883479479994</v>
+        <v>-0.2699339871188482</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.40128383372086074</v>
+        <v>-0.4082025205091514</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.52305563453068049</v>
+        <v>-0.53207383512603701</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.18</v>
+        <v>-1.1599999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18603,7 +18603,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.18</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.18</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21435619529683625</v>
+        <v>0.2212955241882848</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC0DB37-E18A-4073-A3C7-FC25F5FD811C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C387649-C821-4A10-B54D-F968E14DC4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2480,7 +2480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2498,6 +2498,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3146,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3818,36 +3819,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3862,10 +3840,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3877,6 +3851,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4377,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4583,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,19 +4626,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>33649.992691562977</v>
       </c>
@@ -4636,19 +4652,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
@@ -4661,7 +4677,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
@@ -4671,19 +4687,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4693,19 +4709,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>6970.1947987154417</v>
       </c>
@@ -4720,7 +4736,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-11410</v>
       </c>
@@ -4735,7 +4751,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-4439.8052012845583</v>
       </c>
@@ -4753,7 +4769,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
@@ -4763,19 +4779,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-7302.5468725696046</v>
       </c>
@@ -4785,19 +4801,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4807,28 +4823,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>-67214.805201284558</v>
       </c>
@@ -4841,7 +4857,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>21907.640617708814</v>
       </c>
@@ -4880,10 +4896,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4905,11 +4921,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>2.8327145387125552E-2</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>2.4111564983485257E-2</v>
       </c>
@@ -4919,11 +4935,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.11998888979909481</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.11998888979909481</v>
       </c>
@@ -4933,11 +4949,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.0970574812713703</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.0970574812713703</v>
       </c>
@@ -4957,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,19 +5103,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>115864</v>
       </c>
@@ -5125,7 +5141,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>1.4790654865358754E-2</v>
       </c>
@@ -5134,7 +5150,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>3.4432102574884196</v>
       </c>
@@ -5148,7 +5164,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>5072413</v>
       </c>
@@ -5161,7 +5177,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>4573651.4963457817</v>
       </c>
@@ -5192,7 +5208,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>23866.7</v>
       </c>
@@ -5215,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5790,13 +5806,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5819,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6014,339 +6030,339 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>1031173</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>867764</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>924200</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>1198013</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>1028541</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>699593</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>382733</v>
       </c>
-      <c r="J4" s="334"/>
-      <c r="K4" s="334"/>
-      <c r="L4" s="334"/>
-      <c r="M4" s="334"/>
+      <c r="J4" s="321"/>
+      <c r="K4" s="321"/>
+      <c r="L4" s="321"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>313900</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>341249</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>149665</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>270763</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>398163</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>336621</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>189207</v>
       </c>
-      <c r="J5" s="334"/>
-      <c r="K5" s="334"/>
-      <c r="L5" s="334"/>
-      <c r="M5" s="334"/>
+      <c r="J5" s="321"/>
+      <c r="K5" s="321"/>
+      <c r="L5" s="321"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>357132</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>345571</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>398159</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>356401</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>196214</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>150727</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>103615</v>
       </c>
-      <c r="J6" s="334"/>
-      <c r="K6" s="334"/>
-      <c r="L6" s="334"/>
-      <c r="M6" s="334"/>
+      <c r="J6" s="321"/>
+      <c r="K6" s="321"/>
+      <c r="L6" s="321"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>149012</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>137835</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>162582</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>136252</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>86208</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>68142</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>42790</v>
       </c>
-      <c r="J7" s="335"/>
-      <c r="K7" s="335"/>
-      <c r="L7" s="335"/>
-      <c r="M7" s="335"/>
+      <c r="J7" s="322"/>
+      <c r="K7" s="322"/>
+      <c r="L7" s="322"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>330838</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>365801</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>351118</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>277409</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>103725</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>59876</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>41293</v>
       </c>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>11410</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>8305</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>30280</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>135144</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>140407</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>108297</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>75176</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>70887</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>126188</v>
       </c>
-      <c r="E13" s="334"/>
-      <c r="F13" s="334"/>
-      <c r="G13" s="334"/>
-      <c r="H13" s="334"/>
-      <c r="I13" s="334"/>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="E13" s="321"/>
+      <c r="F13" s="321"/>
+      <c r="G13" s="321"/>
+      <c r="H13" s="321"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>92078</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>19417</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>39797</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>75402</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>41042</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>161</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>-6361</v>
       </c>
-      <c r="J14" s="334"/>
-      <c r="K14" s="334"/>
-      <c r="L14" s="334"/>
-      <c r="M14" s="334"/>
+      <c r="J14" s="321"/>
+      <c r="K14" s="321"/>
+      <c r="L14" s="321"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>-835521</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>-443298</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>-21855</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>-12990673</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>-715482</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>-1081974</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>-1410305</v>
       </c>
-      <c r="J15" s="336"/>
-      <c r="K15" s="336"/>
-      <c r="L15" s="336"/>
-      <c r="M15" s="336"/>
+      <c r="J15" s="323"/>
+      <c r="K15" s="323"/>
+      <c r="L15" s="323"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>-140</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>-2058</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>-8397</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>1117</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>1574</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>-336</v>
       </c>
-      <c r="I16" s="334">
-        <v>0</v>
-      </c>
-      <c r="J16" s="334"/>
-      <c r="K16" s="334"/>
-      <c r="L16" s="334"/>
-      <c r="M16" s="334"/>
+      <c r="I16" s="321">
+        <v>0</v>
+      </c>
+      <c r="J16" s="321"/>
+      <c r="K16" s="321"/>
+      <c r="L16" s="321"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6358,139 +6374,139 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334"/>
-      <c r="D19" s="334"/>
-      <c r="E19" s="334"/>
-      <c r="F19" s="334"/>
-      <c r="G19" s="334"/>
-      <c r="H19" s="334"/>
-      <c r="I19" s="334"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="C19" s="321"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>711319</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>-324183</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>1859628</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>-731240</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>2099875</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>201823</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>-991306</v>
       </c>
-      <c r="J22" s="334"/>
-      <c r="K22" s="334"/>
-      <c r="L22" s="334"/>
-      <c r="M22" s="334"/>
+      <c r="J22" s="321"/>
+      <c r="K22" s="321"/>
+      <c r="L22" s="321"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-12356</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-155180</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-274578</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-312659</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-111290</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-94182</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-122694</v>
       </c>
-      <c r="J23" s="334"/>
-      <c r="K23" s="334"/>
-      <c r="L23" s="334"/>
-      <c r="M23" s="334"/>
+      <c r="J23" s="321"/>
+      <c r="K23" s="321"/>
+      <c r="L23" s="321"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-486204</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-535872</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-774277</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>5340309</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>2401986</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-233410</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>1607878</v>
       </c>
-      <c r="J24" s="334"/>
-      <c r="K24" s="334"/>
-      <c r="L24" s="334"/>
-      <c r="M24" s="334"/>
+      <c r="J24" s="321"/>
+      <c r="K24" s="321"/>
+      <c r="L24" s="321"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6535,156 +6551,156 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>218642</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>290847</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>342114</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>254075</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>225175</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>152761</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>56051</v>
       </c>
-      <c r="J28" s="334"/>
-      <c r="K28" s="334"/>
-      <c r="L28" s="334"/>
-      <c r="M28" s="334"/>
+      <c r="J28" s="321"/>
+      <c r="K28" s="321"/>
+      <c r="L28" s="321"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>0</v>
       </c>
-      <c r="D29" s="334">
-        <v>0</v>
-      </c>
-      <c r="E29" s="334">
-        <v>0</v>
-      </c>
-      <c r="F29" s="334">
-        <v>0</v>
-      </c>
-      <c r="G29" s="334">
-        <v>0</v>
-      </c>
-      <c r="H29" s="334">
-        <v>0</v>
-      </c>
-      <c r="I29" s="334">
-        <v>0</v>
-      </c>
-      <c r="J29" s="334"/>
-      <c r="K29" s="334"/>
-      <c r="L29" s="334"/>
-      <c r="M29" s="334"/>
+      <c r="D29" s="321">
+        <v>0</v>
+      </c>
+      <c r="E29" s="321">
+        <v>0</v>
+      </c>
+      <c r="F29" s="321">
+        <v>0</v>
+      </c>
+      <c r="G29" s="321">
+        <v>0</v>
+      </c>
+      <c r="H29" s="321">
+        <v>0</v>
+      </c>
+      <c r="I29" s="321">
+        <v>0</v>
+      </c>
+      <c r="J29" s="321"/>
+      <c r="K29" s="321"/>
+      <c r="L29" s="321"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>760309</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>617731</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>1967828</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>2086158</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>9460292</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>6362095</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>4669537</v>
       </c>
-      <c r="J30" s="336"/>
-      <c r="K30" s="336"/>
-      <c r="L30" s="336"/>
-      <c r="M30" s="336"/>
+      <c r="J30" s="323"/>
+      <c r="K30" s="323"/>
+      <c r="L30" s="323"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>7833595</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>9112791</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>9956528</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>9722107</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>-3323489</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>-2590443</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>-1541033</v>
       </c>
-      <c r="J31" s="336"/>
-      <c r="K31" s="336"/>
-      <c r="L31" s="336"/>
-      <c r="M31" s="336"/>
+      <c r="J31" s="323"/>
+      <c r="K31" s="323"/>
+      <c r="L31" s="323"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>-518</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>-2780</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>-771</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>7529</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>6412</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>4838</v>
       </c>
-      <c r="I32" s="334">
-        <v>0</v>
-      </c>
-      <c r="J32" s="334"/>
-      <c r="K32" s="334"/>
-      <c r="L32" s="334"/>
-      <c r="M32" s="334"/>
+      <c r="I32" s="321">
+        <v>0</v>
+      </c>
+      <c r="J32" s="321"/>
+      <c r="K32" s="321"/>
+      <c r="L32" s="321"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6711,47 +6727,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>1031173</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>867764</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>924200</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>1198013</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>1028541</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>699593</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>382733</v>
       </c>
-      <c r="J36" s="323" t="str">
+      <c r="J36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="323" t="str">
+      <c r="K36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L36" s="323" t="str">
+      <c r="L36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6760,47 +6776,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-313900</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-341249</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-149665</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-270763</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-398163</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-336621</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-189207</v>
       </c>
-      <c r="J37" s="323" t="str">
+      <c r="J37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="323" t="str">
+      <c r="K37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L37" s="323" t="str">
+      <c r="L37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6809,47 +6825,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>717273</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>526515</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>774535</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>927250</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>630378</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>362972</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>193526</v>
       </c>
-      <c r="J38" s="319" t="str">
+      <c r="J38" s="317" t="str">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v/>
       </c>
-      <c r="K38" s="319" t="str">
+      <c r="K38" s="317" t="str">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v/>
       </c>
-      <c r="L38" s="319" t="str">
+      <c r="L38" s="317" t="str">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6858,47 +6874,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-357132</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-345571</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-398159</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-356401</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-196214</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-150727</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-103615</v>
       </c>
-      <c r="J39" s="323" t="str">
+      <c r="J39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K39" s="323" t="str">
+      <c r="K39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="L39" s="323" t="str">
+      <c r="L39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -6907,47 +6923,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-149012</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-137835</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-162582</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-136252</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-86208</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-68142</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-42790</v>
       </c>
-      <c r="J40" s="333" t="str">
+      <c r="J40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K40" s="333" t="str">
+      <c r="K40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L40" s="333" t="str">
+      <c r="L40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -6956,47 +6972,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-208120</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-207736</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-235577</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-220149</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-110006</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-82585</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-60825</v>
       </c>
-      <c r="J41" s="333" t="str">
+      <c r="J41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K41" s="333" t="str">
+      <c r="K41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="L41" s="333" t="str">
+      <c r="L41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7005,47 +7021,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-330838</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-365801</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-351118</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-277409</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-103725</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-59876</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-41293</v>
       </c>
-      <c r="J42" s="323" t="str">
+      <c r="J42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="K42" s="323" t="str">
+      <c r="K42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="L42" s="323" t="str">
+      <c r="L42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7054,47 +7070,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>29303</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>-184857</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>25258</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>293440</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>330439</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>152369</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>48618</v>
       </c>
-      <c r="J43" s="324" t="str">
+      <c r="J43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="K43" s="324" t="str">
+      <c r="K43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="L43" s="324" t="str">
+      <c r="L43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7201,47 +7217,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-92078</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-19417</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-39797</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-75402</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-41042</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-161</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>6361</v>
       </c>
-      <c r="J46" s="323" t="str">
+      <c r="J46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K46" s="323" t="str">
+      <c r="K46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L46" s="323" t="str">
+      <c r="L46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7250,47 +7266,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>-835521</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>-443298</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>-21855</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>-12990673</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>-715482</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>-1081974</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>-1410305</v>
       </c>
-      <c r="J47" s="324" t="str">
+      <c r="J47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="K47" s="324" t="str">
+      <c r="K47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="L47" s="324" t="str">
+      <c r="L47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7299,47 +7315,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-1117</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-1574</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323" t="str">
+      <c r="J48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K48" s="323" t="str">
+      <c r="K48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L48" s="323" t="str">
+      <c r="L48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7353,47 +7369,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-11410</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-8305</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-30280</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-135144</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-140407</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-108297</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-75176</v>
       </c>
-      <c r="J51" s="323" t="str">
+      <c r="J51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K51" s="323" t="str">
+      <c r="K51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L51" s="323" t="str">
+      <c r="L51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7402,47 +7418,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>70887</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>126188</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J52" s="323" t="str">
+      <c r="J52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K52" s="323" t="str">
+      <c r="K52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="L52" s="323" t="str">
+      <c r="L52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7658,47 +7674,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>0</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J61" s="323" t="str">
+      <c r="J61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="K61" s="323" t="str">
+      <c r="K61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="L61" s="323" t="str">
+      <c r="L61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7707,47 +7723,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J62" s="323" t="str">
+      <c r="J62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="K62" s="323" t="str">
+      <c r="K62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="L62" s="323" t="str">
+      <c r="L62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7756,47 +7772,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323" t="str">
+      <c r="J63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="K63" s="323" t="str">
+      <c r="K63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="L63" s="323" t="str">
+      <c r="L63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7805,47 +7821,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>212759</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>-1015235</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>810773</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>4296410</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>4390571</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>-125769</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>493878</v>
       </c>
-      <c r="J64" s="323" t="str">
+      <c r="J64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="K64" s="323" t="str">
+      <c r="K64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="L64" s="323" t="str">
+      <c r="L64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8227,115 +8243,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>218642</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>290847</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>342114</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>254075</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>225175</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>152761</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>760309</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>617731</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>1967828</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>2086158</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>9460292</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>6362095</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>4669537</v>
       </c>
-      <c r="J79" s="323" t="str">
+      <c r="J79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="K79" s="323" t="str">
+      <c r="K79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="L79" s="323" t="str">
+      <c r="L79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8344,47 +8360,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>7833595</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>9112791</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>9956528</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>9722107</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>-3323489</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>-2590443</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>-1541033</v>
       </c>
-      <c r="J80" s="323" t="str">
+      <c r="J80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="K80" s="323" t="str">
+      <c r="K80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="L80" s="323" t="str">
+      <c r="L80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9467,11 +9483,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-83489.166666666672</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-83126.91727570309</v>
       </c>
@@ -9499,8 +9515,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>498761.50365421851</v>
       </c>
@@ -9804,54 +9820,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>G4</f>
         <v>1031173</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>1031173</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>867764</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>924200</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>1198013</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>1028541</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>699593</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>382733</v>
       </c>
-      <c r="N4" s="323" t="str">
+      <c r="N4" s="339" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O4" s="323" t="str">
+      <c r="O4" s="339" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P4" s="323" t="str">
+      <c r="P4" s="339" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9861,52 +9877,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-448336.00730843702</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-462912</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-479084</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-312247</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-407015</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-484371</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-404763</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-231997</v>
       </c>
-      <c r="N5" s="323" t="str">
+      <c r="N5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="O5" s="323" t="str">
+      <c r="O5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P5" s="323" t="str">
+      <c r="P5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9916,52 +9932,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>582836.99269156298</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>568261</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>388680</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>611953</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>790998</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>544170</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>294830</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>150736</v>
       </c>
-      <c r="N6" s="319" t="str">
+      <c r="N6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O6" s="319" t="str">
+      <c r="O6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P6" s="319" t="str">
+      <c r="P6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9971,52 +9987,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-549187</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-538958</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-573537</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-586695</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-497558</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-213731</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-142461</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-102118</v>
       </c>
-      <c r="N7" s="318" t="str">
+      <c r="N7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O7" s="318" t="str">
+      <c r="O7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P7" s="318" t="str">
+      <c r="P7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10026,54 +10042,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>33649.992691562977</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>29303</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>-184857</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>25258</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>293440</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>330439</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>152369</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>48618</v>
       </c>
-      <c r="N8" s="319" t="str">
+      <c r="N8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O8" s="319" t="str">
+      <c r="O8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P8" s="319" t="str">
+      <c r="P8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10083,52 +10099,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="318" t="str">
+      <c r="N9" s="334" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v/>
       </c>
-      <c r="O9" s="318" t="str">
+      <c r="O9" s="334" t="str">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v/>
       </c>
-      <c r="P9" s="318" t="str">
+      <c r="P9" s="334" t="str">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v/>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10138,52 +10154,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>0</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>0</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>0</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>0</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>0</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>0</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>0</v>
       </c>
-      <c r="N10" s="318" t="str">
+      <c r="N10" s="334" t="str">
         <f>Data!J62</f>
         <v/>
       </c>
-      <c r="O10" s="318" t="str">
+      <c r="O10" s="334" t="str">
         <f>Data!K62</f>
         <v/>
       </c>
-      <c r="P10" s="318" t="str">
+      <c r="P10" s="334" t="str">
         <f>Data!L62</f>
         <v/>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10193,54 +10209,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324" t="str">
+      <c r="N11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O11" s="324" t="str">
+      <c r="O11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P11" s="324" t="str">
+      <c r="P11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10250,52 +10266,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-4439.8052012845583</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-4439.8052012845583</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>4102.8454619366621</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-30280</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-135144</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-140407</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-108297</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-75176</v>
       </c>
-      <c r="N12" s="318" t="str">
+      <c r="N12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O12" s="318" t="str">
+      <c r="O12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P12" s="318" t="str">
+      <c r="P12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10305,52 +10321,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>29210.187490278418</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>24863.194798715442</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>-180754.15453806333</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>-5022</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>158296</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>190032</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>44072</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>-26558</v>
       </c>
-      <c r="N13" s="319" t="str">
+      <c r="N13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="O13" s="319" t="str">
+      <c r="O13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P13" s="319" t="str">
+      <c r="P13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10360,52 +10376,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-7302.5468725696046</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-92078</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-19417</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-39797</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-75402</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-41042</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-161</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>6361</v>
       </c>
-      <c r="N14" s="318" t="str">
+      <c r="N14" s="334" t="str">
         <f>Data!J46</f>
         <v/>
       </c>
-      <c r="O14" s="318" t="str">
+      <c r="O14" s="334" t="str">
         <f>Data!K46</f>
         <v/>
       </c>
-      <c r="P14" s="318" t="str">
+      <c r="P14" s="334" t="str">
         <f>Data!L46</f>
         <v/>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10415,54 +10431,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-1117</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-1574</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323" t="str">
+      <c r="N15" s="339" t="str">
         <f>Data!J48</f>
         <v/>
       </c>
-      <c r="O15" s="323" t="str">
+      <c r="O15" s="339" t="str">
         <f>Data!K48</f>
         <v/>
       </c>
-      <c r="P15" s="323" t="str">
+      <c r="P15" s="339" t="str">
         <f>Data!L48</f>
         <v/>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10472,54 +10488,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>21907.640617708814</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>-67214.805201284558</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>-200171.15453806333</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>-44819</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>81777</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>147416</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>43911</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>-20197</v>
       </c>
-      <c r="N16" s="319" t="str">
+      <c r="N16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="O16" s="319" t="str">
+      <c r="O16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P16" s="319" t="str">
+      <c r="P16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10529,7 +10545,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10538,24 +10554,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10563,71 +10579,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>21907.640617708814</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>-67214.805201284558</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>-200171.15453806333</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>-44819</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>81777</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>147416</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>43911</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>-20197</v>
       </c>
-      <c r="N19" s="324" t="str">
+      <c r="N19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O19" s="324" t="str">
+      <c r="O19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P19" s="324" t="str">
+      <c r="P19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10700,54 +10716,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-295465.98495177622</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-313900</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-341249</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-149665</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-270763</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-398163</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-336621</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-189207</v>
       </c>
-      <c r="N23" s="323" t="str">
+      <c r="N23" s="339" t="str">
         <f>Data!J37</f>
         <v/>
       </c>
-      <c r="O23" s="323" t="str">
+      <c r="O23" s="339" t="str">
         <f>Data!K37</f>
         <v/>
       </c>
-      <c r="P23" s="323" t="str">
+      <c r="P23" s="339" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10757,54 +10773,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-152870.0223566608</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-149012</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-137835</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-162582</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-136252</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-86208</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-68142</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-42790</v>
       </c>
-      <c r="N24" s="323" t="str">
+      <c r="N24" s="339" t="str">
         <f>Data!J40</f>
         <v/>
       </c>
-      <c r="O24" s="323" t="str">
+      <c r="O24" s="339" t="str">
         <f>Data!K40</f>
         <v/>
       </c>
-      <c r="P24" s="323" t="str">
+      <c r="P24" s="339" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10814,54 +10830,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-448336.00730843702</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-462912</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-479084</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-312247</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-407015</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-484371</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-404763</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-231997</v>
       </c>
-      <c r="N25" s="319" t="str">
+      <c r="N25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O25" s="319" t="str">
+      <c r="O25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P25" s="319" t="str">
+      <c r="P25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11067,54 +11083,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-217895.5</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-208120</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-207736</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-235577</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-220149</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-110006</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-82585</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-60825</v>
       </c>
-      <c r="N33" s="318" t="str">
+      <c r="N33" s="334" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O33" s="318" t="str">
+      <c r="O33" s="334" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P33" s="318" t="str">
+      <c r="P33" s="334" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11124,7 +11140,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>-331291.5</v>
       </c>
@@ -11133,47 +11149,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-330838</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-365801</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-351118</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-277409</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-103725</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-59876</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-41293</v>
       </c>
-      <c r="N34" s="323" t="str">
+      <c r="N34" s="339" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O34" s="323" t="str">
+      <c r="O34" s="339" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P34" s="323" t="str">
+      <c r="P34" s="339" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11183,54 +11199,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-549187</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-538958</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-573537</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-586695</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-497558</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-213731</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-142461</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-102118</v>
       </c>
-      <c r="N35" s="319" t="str">
+      <c r="N35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O35" s="319" t="str">
+      <c r="O35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P35" s="319" t="str">
+      <c r="P35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11524,52 +11540,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-11410</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-11410</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-8305</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-30280</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-135144</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-140407</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-108297</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-75176</v>
       </c>
-      <c r="N47" s="318" t="str">
+      <c r="N47" s="334" t="str">
         <f>Data!J51</f>
         <v/>
       </c>
-      <c r="O47" s="318" t="str">
+      <c r="O47" s="334" t="str">
         <f>Data!K51</f>
         <v/>
       </c>
-      <c r="P47" s="318" t="str">
+      <c r="P47" s="334" t="str">
         <f>Data!L51</f>
         <v/>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11579,52 +11595,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>6970.1947987154417</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>6970.1947987154417</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>12407.845461936662</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="327" t="str">
+      <c r="N48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="327" t="str">
+      <c r="O48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="327" t="str">
+      <c r="P48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11634,54 +11650,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>70887</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>70887</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>126188</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="329" t="str">
+      <c r="N49" s="348" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="329" t="str">
+      <c r="O49" s="348" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="329" t="str">
+      <c r="P49" s="348" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11691,52 +11707,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-4439.8052012845583</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-4439.8052012845583</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>4102.8454619366621</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-30280</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-135144</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-140407</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-108297</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-75176</v>
       </c>
-      <c r="N50" s="319" t="str">
+      <c r="N50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O50" s="319" t="str">
+      <c r="O50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="P50" s="319" t="str">
+      <c r="P50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11883,52 +11899,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318" t="str">
+      <c r="N58" s="334" t="str">
         <f>Data!J56</f>
         <v/>
       </c>
-      <c r="O58" s="318" t="str">
+      <c r="O58" s="334" t="str">
         <f>Data!K56</f>
         <v/>
       </c>
-      <c r="P58" s="318" t="str">
+      <c r="P58" s="334" t="str">
         <f>Data!L56</f>
         <v/>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -11938,52 +11954,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318" t="str">
+      <c r="N59" s="334" t="str">
         <f>Data!J55</f>
         <v/>
       </c>
-      <c r="O59" s="318" t="str">
+      <c r="O59" s="334" t="str">
         <f>Data!K55</f>
         <v/>
       </c>
-      <c r="P59" s="318" t="str">
+      <c r="P59" s="334" t="str">
         <f>Data!L55</f>
         <v/>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -11993,52 +12009,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318" t="str">
+      <c r="N60" s="334" t="str">
         <f>Data!J57</f>
         <v/>
       </c>
-      <c r="O60" s="318" t="str">
+      <c r="O60" s="334" t="str">
         <f>Data!K57</f>
         <v/>
       </c>
-      <c r="P60" s="318" t="str">
+      <c r="P60" s="334" t="str">
         <f>Data!L57</f>
         <v/>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12048,52 +12064,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319" t="str">
+      <c r="N61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="O61" s="319" t="str">
+      <c r="O61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="P61" s="319" t="str">
+      <c r="P61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12103,53 +12119,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-832223</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>-356907</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>22964</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>-13073567</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-864472</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>-1125885</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>-1390108</v>
       </c>
-      <c r="N62" s="318" t="str">
+      <c r="N62" s="334" t="str">
         <f>Data!J58</f>
         <v/>
       </c>
-      <c r="O62" s="318" t="str">
+      <c r="O62" s="334" t="str">
         <f>Data!K58</f>
         <v/>
       </c>
-      <c r="P62" s="318" t="str">
+      <c r="P62" s="334" t="str">
         <f>Data!L58</f>
         <v/>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12159,52 +12175,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-832223</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>-356907</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>22964</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>-13073567</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>-864472</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>-1125885</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>-1390108</v>
       </c>
-      <c r="N63" s="319" t="str">
+      <c r="N63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="O63" s="319" t="str">
+      <c r="O63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="P63" s="319" t="str">
+      <c r="P63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13579,54 +13595,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>8593904</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>8593904</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>9730522</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>11924356</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>11808265</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>6136803</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>3771652</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>3128504</v>
       </c>
-      <c r="N101" s="323" t="str">
+      <c r="N101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="323" t="str">
+      <c r="O101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="323" t="str">
+      <c r="P101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13636,54 +13652,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>218642</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>290847</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>342114</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>254075</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>225175</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>152761</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333" t="str">
+      <c r="N102" s="352" t="str">
         <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
-      <c r="O102" s="333" t="str">
+      <c r="O102" s="352" t="str">
         <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
-      <c r="P102" s="333" t="str">
+      <c r="P102" s="352" t="str">
         <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13693,54 +13709,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>0</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>0</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>0</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>0</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333" t="str">
+      <c r="N103" s="352" t="str">
         <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
-      <c r="O103" s="333" t="str">
+      <c r="O103" s="352" t="str">
         <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
-      <c r="P103" s="333" t="str">
+      <c r="P103" s="352" t="str">
         <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13750,54 +13766,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>760309</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>760309</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>617731</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>1967828</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>2086158</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>9460292</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>6362095</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>4669537</v>
       </c>
-      <c r="N104" s="323" t="str">
+      <c r="N104" s="339" t="str">
         <f>Data!J79</f>
         <v/>
       </c>
-      <c r="O104" s="323" t="str">
+      <c r="O104" s="339" t="str">
         <f>Data!K79</f>
         <v/>
       </c>
-      <c r="P104" s="323" t="str">
+      <c r="P104" s="339" t="str">
         <f>Data!L79</f>
         <v/>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13807,54 +13823,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>7833595</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>7833595</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>9112791</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>9956528</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>9722107</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>-3323489</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>-2590443</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>-1541033</v>
       </c>
-      <c r="N105" s="323" t="str">
+      <c r="N105" s="339" t="str">
         <f>Data!J80</f>
         <v/>
       </c>
-      <c r="O105" s="323" t="str">
+      <c r="O105" s="339" t="str">
         <f>Data!K80</f>
         <v/>
       </c>
-      <c r="P105" s="323" t="str">
+      <c r="P105" s="339" t="str">
         <f>Data!L80</f>
         <v/>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15352,7 +15368,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15391,7 +15407,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>21907.640617708814</v>
       </c>
@@ -15423,7 +15439,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>292101.87490278418</v>
       </c>
@@ -15431,17 +15447,17 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>115864</v>
       </c>
@@ -15449,15 +15465,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>4573651.4963457817</v>
       </c>
@@ -15465,15 +15481,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>23866.7</v>
       </c>
@@ -15481,15 +15497,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>4773756.0712485658</v>
       </c>
@@ -15556,7 +15572,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15566,7 +15582,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15580,10 +15596,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15601,7 +15617,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15623,7 +15639,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15645,7 +15661,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15665,9 +15681,19 @@
         <f t="shared" si="1"/>
         <v>20215.343417386746</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15687,9 +15713,19 @@
         <f t="shared" si="1"/>
         <v>19680.809699581539</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15709,9 +15745,19 @@
         <f t="shared" si="1"/>
         <v>19160.410111955138</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15733,7 +15779,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15755,7 +15801,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15777,7 +15823,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15799,7 +15845,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15821,7 +15867,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15843,7 +15889,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15865,11 +15911,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15885,13 +15931,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15907,13 +15963,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15929,9 +15995,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -15953,7 +16029,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -15975,7 +16051,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -15997,7 +16073,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16019,7 +16095,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16041,7 +16117,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16063,7 +16139,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16085,7 +16161,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16107,7 +16183,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16129,7 +16205,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16151,7 +16227,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16173,11 +16249,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16193,13 +16269,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16215,13 +16301,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16237,13 +16333,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16259,9 +16365,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16283,7 +16399,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16294,11 +16410,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16308,7 +16424,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>337941.38254475768</v>
@@ -16335,7 +16451,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16357,7 +16473,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16378,14 +16494,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>164231.2612386971</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>292101.87490278424</v>
       </c>
       <c r="D58" s="123">
@@ -16397,16 +16513,26 @@
       <c r="F58" s="123">
         <v>701400.51267742459</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>140456.96258364385</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>292101.87490278424</v>
       </c>
       <c r="D59" s="123">
@@ -16418,16 +16544,26 @@
       <c r="F59" s="123">
         <v>1037416.7285353488</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>123242.60416404021</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>292101.8749027843</v>
       </c>
       <c r="D60" s="123">
@@ -16439,16 +16575,26 @@
       <c r="F60" s="123">
         <v>1532453.3884392621</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>111049.61340254245</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>292101.8749027843</v>
       </c>
       <c r="D61" s="123">
@@ -16460,26 +16606,56 @@
       <c r="F61" s="123">
         <v>2242918.121417555</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.15</v>
@@ -16851,6 +17027,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16953,7 +17199,7 @@
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>0</v>
       </c>
@@ -16961,8 +17207,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18419,7 +18665,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>29303</v>
       </c>
@@ -18427,11 +18673,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 聯易融科技(9959.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18444,7 +18690,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>-67214.805201284558</v>
       </c>
@@ -18452,8 +18698,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18466,7 +18712,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>21907.640617708814</v>
       </c>
@@ -18474,8 +18720,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18485,8 +18731,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18499,8 +18745,8 @@
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18518,8 +18764,8 @@
         <v>-4.8760226650597205E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18536,8 +18782,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.53605739463275559</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18554,8 +18800,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9367231569408296</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18581,21 +18827,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18609,8 +18855,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18624,8 +18870,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18645,8 +18891,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18656,8 +18902,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18671,8 +18917,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18682,8 +18928,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18703,8 +18949,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18714,8 +18960,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18729,8 +18975,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18740,8 +18986,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18761,8 +19007,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18772,8 +19018,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18787,8 +19033,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18799,8 +19045,8 @@
         <v>0.3</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18862,8 +19108,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18873,8 +19119,8 @@
         <v>-0.15</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18888,8 +19134,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18899,8 +19145,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -18920,8 +19166,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -18931,8 +19177,8 @@
         <v>0.15</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -18946,8 +19192,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -18957,8 +19203,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C387649-C821-4A10-B54D-F968E14DC4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E66B5D-A394-4631-8B74-C52CFA81EF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,29 +3895,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4335,7 +4335,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2650.5813796799998</v>
+        <v>2627.7315401999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4393,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2212955241882848</v>
+        <v>0.22482529966657938</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4599,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4626,13 +4626,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4652,13 +4652,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4687,13 +4687,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4709,13 +4709,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4779,13 +4779,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4801,7 +4801,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4823,22 +4823,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.265220900462859E-3</v>
+        <v>8.3370923865538401E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5032,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5084,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5103,13 +5103,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5231,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5276,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5425,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5444,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5792,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5835,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5849,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5888,17 +5888,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5915,6 +5904,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14566,38 +14566,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.265220900462859E-3</v>
+        <v>8.3370923865538401E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.535851406660047E-2</v>
+        <v>-2.5579022884570909E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.5519716569588835E-2</v>
+        <v>-7.6176409757150482E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.6909120521102779E-2</v>
+        <v>-1.7056156351721065E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.0852476602651148E-2</v>
+        <v>3.1120759007891595E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5616477626428233E-2</v>
+        <v>5.610009917100587E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6566554166807471E-2</v>
+        <v>1.6710611159562322E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.6198377287470228E-3</v>
+        <v>-7.6860971872578666E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14623,31 +14623,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31522178734269651</v>
+        <v>-0.31796284636306776</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16724557238590373</v>
+        <v>-0.16869988171099856</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.2453608734844863E-3</v>
+        <v>-8.3170596636886994E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.901065517018135</v>
+        <v>-4.943683478035684</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.2699339871188482</v>
+        <v>-0.27228123918075126</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.4082025205091514</v>
+        <v>-0.4117521076440136</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.53207383512603701</v>
+        <v>-0.53670056412713296</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.1599999999999999</v>
+        <v>-1.1499999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19460,7 +19460,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2212955241882848</v>
+        <v>0.22482529966657938</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243542C8-01D6-412B-AEB7-41F1755665E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDE3D36-8013-8847-BCEF-215A34FBDBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2510,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3891,30 +3902,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3929,7 +3940,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4218,16 +4229,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4244,7 +4255,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4258,7 +4269,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>414</v>
       </c>
@@ -4267,7 +4278,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4275,7 +4286,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4284,7 +4295,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4294,7 +4305,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4304,17 +4315,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>417</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>416</v>
       </c>
@@ -4326,17 +4337,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>415</v>
       </c>
@@ -4346,13 +4357,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>419</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2673.4312191599997</v>
+        <v>2696.2810586400001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4360,7 +4371,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>418</v>
       </c>
@@ -4374,7 +4385,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4384,27 +4395,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4419,7 +4430,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4432,7 +4443,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>433</v>
       </c>
@@ -4440,7 +4451,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>434</v>
       </c>
@@ -4448,7 +4459,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4464,7 +4475,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -4478,14 +4489,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21780608938756418</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.21435619529683625</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>432</v>
       </c>
@@ -4504,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>424</v>
       </c>
@@ -4523,7 +4534,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>425</v>
       </c>
@@ -4542,7 +4553,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>426</v>
       </c>
@@ -4561,7 +4572,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>427</v>
       </c>
@@ -4580,11 +4591,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4594,25 +4605,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4621,16 +4632,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4643,20 +4654,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4682,16 +4693,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4704,16 +4715,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4728,7 +4739,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4743,7 +4754,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4756,12 +4767,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4774,16 +4785,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4796,8 +4807,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4805,7 +4816,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4818,25 +4829,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4849,7 +4860,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4862,17 +4873,17 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.1945779867836892E-3</v>
+        <v>8.1251324106245051E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
@@ -4888,7 +4899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4899,7 +4910,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4912,7 +4923,7 @@
         <v>3.1739188455256421E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4926,7 +4937,7 @@
         <v>2.4111564983485257E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4940,7 +4951,7 @@
         <v>0.11998888979909481</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4954,7 +4965,7 @@
         <v>1.0970574812713703</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4964,34 +4975,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>430</v>
       </c>
@@ -5000,7 +5011,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>429</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5018,34 +5029,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5053,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5066,7 +5077,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5076,38 +5087,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5120,7 +5131,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5133,7 +5144,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5142,7 +5153,7 @@
         <v>1.4790654865358754E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5151,12 +5162,12 @@
         <v>3.4432102574884196</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5169,7 +5180,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5182,7 +5193,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5195,12 +5206,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5213,7 +5224,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5226,16 +5237,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>448</v>
       </c>
@@ -5248,7 +5259,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5261,7 +5272,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5271,16 +5282,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5297,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5319,7 +5330,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5341,7 +5352,7 @@
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5363,7 +5374,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5385,7 +5396,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5407,7 +5418,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5420,16 +5431,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5439,30 +5450,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5471,7 +5482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5480,7 +5491,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5493,7 +5504,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5506,7 +5517,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5515,7 +5526,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5525,7 +5536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5535,7 +5546,7 @@
         <v>0.82648230361166808</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5548,7 +5559,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>415</v>
       </c>
@@ -5561,7 +5572,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5570,12 +5581,12 @@
         <v>0.60887707393464918</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5584,7 +5595,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5594,7 +5605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5604,7 +5615,7 @@
         <v>1.1711712249606363</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5617,7 +5628,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>415</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5639,12 +5650,12 @@
         <v>0.44575713910823733</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5653,7 +5664,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5663,7 +5674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5673,7 +5684,7 @@
         <v>1.7009631025661165</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5686,7 +5697,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>415</v>
       </c>
@@ -5699,7 +5710,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5708,12 +5719,12 @@
         <v>0.19503943049039696</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>422</v>
       </c>
@@ -5722,7 +5733,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5732,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5742,7 +5753,7 @@
         <v>1.514587208466269</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5755,7 +5766,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>415</v>
       </c>
@@ -5768,7 +5779,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5777,7 +5788,7 @@
         <v>0.2819299041708756</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5787,21 +5798,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5810,80 +5821,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5922,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5941,15 +5952,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -5998,7 +6009,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6014,7 +6025,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6022,7 +6033,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6052,7 +6063,7 @@
       <c r="L4" s="351"/>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6082,7 +6093,7 @@
       <c r="L5" s="351"/>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6112,7 +6123,7 @@
       <c r="L6" s="351"/>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6142,7 +6153,7 @@
       <c r="L7" s="352"/>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6172,7 +6183,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6188,7 +6199,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6204,7 +6215,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6220,7 +6231,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6250,7 +6261,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6270,7 +6281,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6300,7 +6311,7 @@
       <c r="L14" s="351"/>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6330,7 +6341,7 @@
       <c r="L15" s="353"/>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6360,13 +6371,13 @@
       <c r="L16" s="351"/>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6382,7 +6393,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6398,7 +6409,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6414,7 +6425,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6444,7 +6455,7 @@
       <c r="L22" s="351"/>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6474,7 +6485,7 @@
       <c r="L23" s="351"/>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6504,7 +6515,7 @@
       <c r="L24" s="351"/>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6535,7 +6546,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6543,7 +6554,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6574,7 +6585,7 @@
       <c r="L28" s="351"/>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6605,7 +6616,7 @@
       <c r="L29" s="351"/>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6636,7 +6647,7 @@
       <c r="L30" s="353"/>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6667,7 +6678,7 @@
       <c r="L31" s="353"/>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6698,7 +6709,7 @@
       <c r="L32" s="351"/>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6714,12 +6725,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6768,7 +6779,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6817,7 +6828,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6866,7 +6877,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6915,7 +6926,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6964,7 +6975,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7013,7 +7024,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7062,7 +7073,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7111,7 +7122,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7160,7 +7171,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7209,7 +7220,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7258,7 +7269,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7307,7 +7318,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7356,12 +7367,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7410,7 +7421,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7459,12 +7470,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7513,7 +7524,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7562,7 +7573,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7611,7 +7622,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7660,13 +7671,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7715,7 +7726,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7764,7 +7775,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7813,7 +7824,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7862,7 +7873,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7911,12 +7922,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7966,7 +7977,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8015,7 +8026,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8065,7 +8076,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8114,7 +8125,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8164,7 +8175,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8180,13 +8191,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8235,7 +8246,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8269,7 +8280,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8303,7 +8314,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8352,7 +8363,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8433,18 +8444,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8460,7 +8471,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8471,7 +8482,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8491,7 +8502,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8512,7 +8523,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8534,7 +8545,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8555,7 +8566,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8576,7 +8587,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8597,7 +8608,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8618,7 +8629,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8630,7 +8641,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8642,7 +8653,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8666,12 +8677,12 @@
         <v>4530366.0999999996</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8691,7 +8702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8711,7 +8722,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8731,7 +8742,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8751,7 +8762,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8771,7 +8782,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8792,7 +8803,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8812,7 +8823,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8832,7 +8843,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8844,7 +8855,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8857,7 +8868,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8881,7 +8892,7 @@
         <v>23866.7</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8898,7 +8909,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8917,7 +8928,7 @@
         <v>4628457.25</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8932,7 +8943,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8951,7 +8962,7 @@
         <v>4628975.25</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8967,7 +8978,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -8984,7 +8995,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9004,7 +9015,7 @@
         <v>5388766.25</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9015,7 +9026,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9028,7 +9039,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9047,7 +9058,7 @@
         <v>834533.45</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9063,7 +9074,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9079,7 +9090,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9095,7 +9106,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9114,7 +9125,7 @@
         <v>10282.200000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9134,7 +9145,7 @@
         <v>4554232.8</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9154,7 +9165,7 @@
         <v>4530366.0999999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9173,7 +9184,7 @@
         <v>23866.7</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9184,7 +9195,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9198,7 +9209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9212,7 +9223,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9227,10 +9238,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9243,7 +9254,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9257,7 +9268,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9268,10 +9279,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9283,7 +9294,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9297,7 +9308,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9311,10 +9322,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9326,7 +9337,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9337,7 +9348,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9348,10 +9359,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9363,7 +9374,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9379,7 +9390,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9390,7 +9401,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9404,7 +9415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9420,7 +9431,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9430,7 +9441,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9440,7 +9451,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9450,7 +9461,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9460,10 +9471,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9475,7 +9486,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9491,7 +9502,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9507,7 +9518,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9520,7 +9531,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9533,10 +9544,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9548,7 +9559,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9562,7 +9573,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9576,7 +9587,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9590,7 +9601,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9604,7 +9615,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9615,7 +9626,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9623,7 +9634,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9640,7 +9651,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9657,7 +9668,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9674,7 +9685,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9705,19 +9716,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9774,7 +9785,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9797,7 +9808,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9811,7 +9822,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9868,7 +9879,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9923,7 +9934,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9978,7 +9989,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10033,7 +10044,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10090,7 +10101,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10145,7 +10156,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10200,7 +10211,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10257,7 +10268,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10312,7 +10323,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10367,7 +10378,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10422,7 +10433,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10479,7 +10490,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10536,7 +10547,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10562,7 +10573,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10587,7 +10598,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10644,7 +10655,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10663,7 +10674,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10686,7 +10697,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10707,7 +10718,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10764,7 +10775,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10821,7 +10832,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10878,18 +10889,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10948,7 +10959,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11008,7 +11019,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11063,18 +11074,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11131,7 +11142,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11190,7 +11201,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11247,18 +11258,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11316,7 +11327,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11374,7 +11385,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11429,18 +11440,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11498,10 +11509,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11524,14 +11535,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11586,7 +11597,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11641,7 +11652,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11698,7 +11709,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11753,11 +11764,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11767,7 +11778,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11794,7 +11805,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11821,7 +11832,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11876,11 +11887,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11890,7 +11901,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -11945,7 +11956,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12000,7 +12011,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12055,7 +12066,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12110,7 +12121,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12166,7 +12177,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12221,11 +12232,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12235,7 +12246,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12260,7 +12271,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12285,7 +12296,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12310,7 +12321,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12337,10 +12348,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12363,7 +12374,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12384,7 +12395,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12441,7 +12452,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12498,7 +12509,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12555,7 +12566,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12612,7 +12623,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12669,7 +12680,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12728,7 +12739,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12785,7 +12796,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12842,7 +12853,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12899,7 +12910,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12956,7 +12967,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13014,7 +13025,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13071,7 +13082,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13097,7 +13108,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13121,7 +13132,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13178,18 +13189,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13245,7 +13256,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13301,7 +13312,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13356,7 +13367,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
@@ -13411,11 +13422,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13436,7 +13447,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13493,7 +13504,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13550,10 +13561,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13576,7 +13587,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13586,7 +13597,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13643,7 +13654,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13700,7 +13711,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13757,7 +13768,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13814,7 +13825,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13871,11 +13882,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13898,7 +13909,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -13955,7 +13966,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14012,7 +14023,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14039,18 +14050,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14102,7 +14113,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14154,11 +14165,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14212,7 +14223,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14267,7 +14278,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14321,7 +14332,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14377,7 +14388,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14434,7 +14445,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14453,7 +14464,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14476,7 +14487,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14497,7 +14508,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14555,45 +14566,45 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1945779867836892E-3</v>
+        <v>8.1251324106245051E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.5141774630133801E-2</v>
+        <v>-2.492870874343775E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.4874248906600896E-2</v>
+        <v>-7.4239721373494119E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.6764598123486515E-2</v>
+        <v>-1.662252525803324E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.058878022143191E-2</v>
+        <v>3.0329553270402824E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5141123116800639E-2</v>
+        <v>5.4673825463268433E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6424959686749289E-2</v>
+        <v>1.6285765113132768E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.5547109105526039E-3</v>
+        <v>-7.4906879367343613E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14612,38 +14623,38 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31252758403207515</v>
+        <v>-0.30987904518434572</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16581612304927207</v>
+        <v>-0.16441090166749858</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.1748877036256443E-3</v>
+        <v>-8.1056089942728848E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8591760681547322</v>
+        <v>-4.8179966099500309</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.26762685902381533</v>
+        <v>-0.26535883479479994</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.40471361007744927</v>
+        <v>-0.40128383372086074</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.52752619550957514</v>
+        <v>-0.52305563453068049</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14662,688 +14673,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15365,16 +15376,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15386,7 +15397,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15399,7 +15410,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15420,7 +15431,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15431,7 +15442,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15449,7 +15460,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15465,7 +15476,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15481,7 +15492,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15497,7 +15508,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15511,7 +15522,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15525,7 +15536,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15539,10 +15550,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15552,13 +15563,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15568,7 +15579,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15578,7 +15589,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15592,10 +15603,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15613,7 +15624,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15635,7 +15646,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15657,7 +15668,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15689,7 +15700,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15721,7 +15732,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15753,7 +15764,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15775,7 +15786,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15797,7 +15808,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15819,7 +15830,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15841,7 +15852,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15863,7 +15874,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15885,7 +15896,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15907,7 +15918,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -15939,7 +15950,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -15971,7 +15982,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16003,7 +16014,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16025,7 +16036,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16047,7 +16058,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16069,7 +16080,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16091,7 +16102,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16113,7 +16124,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16135,7 +16146,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16157,7 +16168,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16179,7 +16190,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16201,7 +16212,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16223,7 +16234,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16245,7 +16256,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16277,7 +16288,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16309,7 +16320,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16341,7 +16352,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16373,7 +16384,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16395,7 +16406,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16406,11 +16417,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16420,7 +16431,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>337941.38254475768</v>
@@ -16447,7 +16458,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16469,7 +16480,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16490,7 +16501,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16521,7 +16532,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16552,7 +16563,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16583,7 +16594,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16614,7 +16625,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16631,7 +16642,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16651,7 +16662,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.15</v>
@@ -16674,7 +16685,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16700,7 +16711,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16727,7 +16738,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16754,7 +16765,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16781,7 +16792,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16808,7 +16819,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16834,7 +16845,7 @@
         <v>2.6320130563932715</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16860,7 +16871,7 @@
         <v>2.9429407255351698</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16877,7 +16888,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16899,7 +16910,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16922,7 +16933,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16945,7 +16956,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16968,7 +16979,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16990,14 +17001,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17005,26 +17016,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17038,7 +17049,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17052,7 +17063,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17066,7 +17077,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17080,7 +17091,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17125,16 +17136,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>442</v>
       </c>
@@ -17146,7 +17157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>441</v>
       </c>
@@ -17159,7 +17170,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>439</v>
       </c>
@@ -17180,7 +17191,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17191,7 +17202,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>440</v>
       </c>
@@ -17207,7 +17218,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>443</v>
       </c>
@@ -17221,10 +17232,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17234,13 +17245,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17250,7 +17261,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17260,7 +17271,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17274,10 +17285,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17295,7 +17306,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17317,7 +17328,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17339,7 +17350,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17361,7 +17372,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17383,7 +17394,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17405,7 +17416,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17427,7 +17438,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17449,7 +17460,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17471,7 +17482,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17493,7 +17504,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17515,7 +17526,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17537,7 +17548,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17559,7 +17570,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17581,7 +17592,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17603,7 +17614,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17625,7 +17636,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17647,7 +17658,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17669,7 +17680,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17691,7 +17702,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17713,7 +17724,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17735,7 +17746,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17757,7 +17768,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17779,7 +17790,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17801,7 +17812,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17823,7 +17834,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17845,7 +17856,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17867,7 +17878,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17889,7 +17900,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -17911,7 +17922,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -17933,7 +17944,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -17955,7 +17966,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -17977,7 +17988,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -17988,11 +17999,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18002,7 +18013,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>0</v>
@@ -18029,7 +18040,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18051,7 +18062,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18072,7 +18083,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18093,7 +18104,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18114,7 +18125,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18135,7 +18146,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18156,14 +18167,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18173,7 +18184,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>-0.15</v>
@@ -18196,7 +18207,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18222,7 +18233,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18249,7 +18260,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18276,7 +18287,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18303,7 +18314,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18330,7 +18341,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18356,7 +18367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18382,7 +18393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18399,7 +18410,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18421,7 +18432,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18444,7 +18455,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18467,7 +18478,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18490,7 +18501,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18512,14 +18523,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18527,23 +18538,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18573,17 +18584,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18596,7 +18607,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18605,10 +18616,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18628,7 +18639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18637,7 +18648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18657,7 +18668,7 @@
         <v>2.1131011468081908</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18682,7 +18693,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18704,7 +18715,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18726,7 +18737,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18737,7 +18748,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>446</v>
       </c>
@@ -18751,7 +18762,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18770,7 +18781,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18788,7 +18799,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18799,7 +18810,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18808,7 +18819,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18816,7 +18827,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18828,24 +18839,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18854,7 +18865,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18869,7 +18880,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18878,7 +18889,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18890,7 +18901,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18901,7 +18912,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -18916,7 +18927,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -18927,7 +18938,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -18936,7 +18947,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -18948,7 +18959,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -18959,7 +18970,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -18974,7 +18985,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -18985,7 +18996,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -18994,7 +19005,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19006,7 +19017,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19017,7 +19028,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19032,7 +19043,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19044,7 +19055,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19057,7 +19068,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19066,12 +19077,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19081,12 +19092,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19095,7 +19106,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19107,7 +19118,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19118,7 +19129,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19133,7 +19144,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19144,7 +19155,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19153,7 +19164,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19165,7 +19176,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19176,7 +19187,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19191,7 +19202,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19202,7 +19213,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19222,7 +19233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19231,7 +19242,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19239,7 +19250,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19252,7 +19263,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19264,7 +19275,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19280,7 +19291,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19288,7 +19299,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19298,7 +19309,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19310,7 +19321,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19320,7 +19331,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19336,7 +19347,7 @@
         <v>0.92818576618522131</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19345,12 +19356,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19360,7 +19371,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19373,12 +19384,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19387,7 +19398,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19399,7 +19410,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19409,7 +19420,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19429,45 +19440,45 @@
         <v>0.60887707393464918</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21780608938756418</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.21435619529683625</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19476,7 +19487,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19488,7 +19499,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19498,7 +19509,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19518,14 +19529,14 @@
         <v>0.44575713910823733</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19536,7 +19547,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19548,7 +19559,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19560,7 +19571,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19579,15 +19590,15 @@
         <v>0.19503943049039696</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>420</v>
       </c>
@@ -19596,7 +19607,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19606,7 +19617,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19616,7 +19627,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19635,16 +19646,16 @@
         <v>0.2819299041708756</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19652,7 +19663,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19660,7 +19671,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDE3D36-8013-8847-BCEF-215A34FBDBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077A1AC5-7721-432B-870A-CD01D321C211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2510,7 +2499,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3902,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3940,7 +3929,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4229,7 +4218,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4238,7 +4227,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4255,7 +4244,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4269,7 +4258,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>414</v>
       </c>
@@ -4278,7 +4267,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4286,7 +4275,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4295,7 +4284,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4305,7 +4294,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4315,17 +4304,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>417</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>416</v>
       </c>
@@ -4337,17 +4326,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>415</v>
       </c>
@@ -4357,13 +4346,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>419</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2696.2810586400001</v>
+        <v>2673.4312191599997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4371,7 +4360,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>418</v>
       </c>
@@ -4385,7 +4374,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4395,27 +4384,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4430,7 +4419,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4443,7 +4432,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>433</v>
       </c>
@@ -4451,7 +4440,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>434</v>
       </c>
@@ -4459,7 +4448,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4475,7 +4464,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -4489,14 +4478,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21435619529683625</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.21780608938756418</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>432</v>
       </c>
@@ -4515,7 +4504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>424</v>
       </c>
@@ -4534,7 +4523,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>425</v>
       </c>
@@ -4553,7 +4542,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>426</v>
       </c>
@@ -4572,7 +4561,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>427</v>
       </c>
@@ -4591,11 +4580,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4605,25 +4594,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4632,16 +4621,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4654,20 +4643,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4680,7 +4669,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4693,16 +4682,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4715,16 +4704,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4739,7 +4728,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4754,7 +4743,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4767,12 +4756,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4785,16 +4774,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4807,8 +4796,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4816,7 +4805,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4829,25 +4818,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4860,7 +4849,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4873,17 +4862,17 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.1251324106245051E-3</v>
+        <v>8.1945779867836892E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
@@ -4899,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4910,7 +4899,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4923,7 +4912,7 @@
         <v>3.1739188455256421E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4937,7 +4926,7 @@
         <v>2.4111564983485257E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4951,7 +4940,7 @@
         <v>0.11998888979909481</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4965,7 +4954,7 @@
         <v>1.0970574812713703</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4975,34 +4964,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>430</v>
       </c>
@@ -5011,7 +5000,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>429</v>
       </c>
@@ -5020,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5029,34 +5018,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5064,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5077,7 +5066,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5087,38 +5076,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5131,7 +5120,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5144,7 +5133,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5153,7 +5142,7 @@
         <v>1.4790654865358754E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5162,12 +5151,12 @@
         <v>3.4432102574884196</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5180,7 +5169,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5206,12 +5195,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5224,7 +5213,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5237,16 +5226,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>448</v>
       </c>
@@ -5259,7 +5248,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5272,7 +5261,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5282,16 +5271,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5308,7 +5297,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5330,7 +5319,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5352,7 +5341,7 @@
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5374,7 +5363,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5396,7 +5385,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5418,7 +5407,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5431,16 +5420,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5450,30 +5439,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5482,7 +5471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5491,7 +5480,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5504,7 +5493,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5517,7 +5506,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5526,7 +5515,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5536,7 +5525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5546,7 +5535,7 @@
         <v>0.82648230361166808</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5559,7 +5548,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>415</v>
       </c>
@@ -5572,7 +5561,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5581,12 +5570,12 @@
         <v>0.60887707393464918</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5595,7 +5584,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5605,7 +5594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5615,7 +5604,7 @@
         <v>1.1711712249606363</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5628,7 +5617,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>415</v>
       </c>
@@ -5641,7 +5630,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5650,12 +5639,12 @@
         <v>0.44575713910823733</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5664,7 +5653,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5674,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5684,7 +5673,7 @@
         <v>1.7009631025661165</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5697,7 +5686,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>415</v>
       </c>
@@ -5710,7 +5699,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5719,12 +5708,12 @@
         <v>0.19503943049039696</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>422</v>
       </c>
@@ -5733,7 +5722,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5743,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5753,7 +5742,7 @@
         <v>1.514587208466269</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5766,7 +5755,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>415</v>
       </c>
@@ -5779,7 +5768,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5788,7 +5777,7 @@
         <v>0.2819299041708756</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5798,21 +5787,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5821,91 +5810,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5922,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5952,15 +5941,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -6009,7 +5998,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6025,7 +6014,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6033,7 +6022,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6063,7 +6052,7 @@
       <c r="L4" s="351"/>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6093,7 +6082,7 @@
       <c r="L5" s="351"/>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6123,7 +6112,7 @@
       <c r="L6" s="351"/>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6153,7 +6142,7 @@
       <c r="L7" s="352"/>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6183,7 +6172,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6199,7 +6188,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6215,7 +6204,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6231,7 +6220,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6261,7 +6250,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6281,7 +6270,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6311,7 +6300,7 @@
       <c r="L14" s="351"/>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6341,7 +6330,7 @@
       <c r="L15" s="353"/>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6371,13 +6360,13 @@
       <c r="L16" s="351"/>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6393,7 +6382,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6409,7 +6398,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6425,7 +6414,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6455,7 +6444,7 @@
       <c r="L22" s="351"/>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6485,7 +6474,7 @@
       <c r="L23" s="351"/>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6515,7 +6504,7 @@
       <c r="L24" s="351"/>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6546,7 +6535,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6554,7 +6543,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6585,7 +6574,7 @@
       <c r="L28" s="351"/>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6616,7 +6605,7 @@
       <c r="L29" s="351"/>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6647,7 +6636,7 @@
       <c r="L30" s="353"/>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6678,7 +6667,7 @@
       <c r="L31" s="353"/>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6709,7 +6698,7 @@
       <c r="L32" s="351"/>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6725,12 +6714,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6779,7 +6768,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6828,7 +6817,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6877,7 +6866,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6926,7 +6915,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6975,7 +6964,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7024,7 +7013,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7073,7 +7062,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7122,7 +7111,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7171,7 +7160,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7220,7 +7209,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7269,7 +7258,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7318,7 +7307,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7367,12 +7356,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7421,7 +7410,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7470,12 +7459,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7524,7 +7513,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7573,7 +7562,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7622,7 +7611,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7671,13 +7660,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7726,7 +7715,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7775,7 +7764,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7824,7 +7813,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7873,7 +7862,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7922,12 +7911,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7977,7 +7966,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8026,7 +8015,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8076,7 +8065,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8125,7 +8114,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8175,7 +8164,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8191,13 +8180,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8246,7 +8235,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8280,7 +8269,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8314,7 +8303,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8363,7 +8352,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8444,7 +8433,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8455,7 +8444,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8471,7 +8460,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8482,7 +8471,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8502,7 +8491,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8523,7 +8512,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8545,7 +8534,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8566,7 +8555,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8587,7 +8576,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8608,7 +8597,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8629,7 +8618,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8641,7 +8630,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8653,7 +8642,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8677,12 +8666,12 @@
         <v>4530366.0999999996</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8702,7 +8691,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8722,7 +8711,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8742,7 +8731,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8762,7 +8751,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8782,7 +8771,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8803,7 +8792,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8823,7 +8812,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8843,7 +8832,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8855,7 +8844,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8868,7 +8857,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8892,7 +8881,7 @@
         <v>23866.7</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8909,7 +8898,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8928,7 +8917,7 @@
         <v>4628457.25</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8943,7 +8932,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8962,7 +8951,7 @@
         <v>4628975.25</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8978,7 +8967,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -8995,7 +8984,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9015,7 +9004,7 @@
         <v>5388766.25</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9026,7 +9015,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9039,7 +9028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9058,7 +9047,7 @@
         <v>834533.45</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9074,7 +9063,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9090,7 +9079,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9106,7 +9095,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9125,7 +9114,7 @@
         <v>10282.200000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9145,7 +9134,7 @@
         <v>4554232.8</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9165,7 +9154,7 @@
         <v>4530366.0999999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9184,7 +9173,7 @@
         <v>23866.7</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9195,7 +9184,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9209,7 +9198,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9223,7 +9212,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9238,10 +9227,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9254,7 +9243,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9268,7 +9257,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9279,10 +9268,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9294,7 +9283,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9308,7 +9297,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9322,10 +9311,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9337,7 +9326,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9348,7 +9337,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9359,10 +9348,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9374,7 +9363,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9390,7 +9379,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9401,7 +9390,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9415,7 +9404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9431,7 +9420,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9441,7 +9430,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9451,7 +9440,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9461,7 +9450,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9471,10 +9460,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9486,7 +9475,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9502,7 +9491,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9518,7 +9507,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9531,7 +9520,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9544,10 +9533,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9559,7 +9548,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9573,7 +9562,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9587,7 +9576,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9601,7 +9590,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9615,7 +9604,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9626,7 +9615,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9634,7 +9623,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9651,7 +9640,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9668,7 +9657,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9685,7 +9674,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9716,19 +9705,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9785,7 +9774,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9808,7 +9797,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9822,7 +9811,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9879,7 +9868,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9934,7 +9923,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9989,7 +9978,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10044,7 +10033,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10101,7 +10090,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10156,7 +10145,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10211,7 +10200,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10268,7 +10257,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10323,7 +10312,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10378,7 +10367,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10433,7 +10422,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10490,7 +10479,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10547,7 +10536,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10573,7 +10562,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10598,7 +10587,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10655,7 +10644,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10674,7 +10663,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10697,7 +10686,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10718,7 +10707,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10775,7 +10764,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10832,7 +10821,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10889,18 +10878,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10959,7 +10948,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11019,7 +11008,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11074,18 +11063,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11142,7 +11131,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11201,7 +11190,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11258,18 +11247,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11327,7 +11316,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11385,7 +11374,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11440,18 +11429,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11509,10 +11498,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11535,14 +11524,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11597,7 +11586,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11652,7 +11641,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11709,7 +11698,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11764,11 +11753,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11778,7 +11767,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11805,7 +11794,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11832,7 +11821,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11887,11 +11876,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11901,7 +11890,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -11956,7 +11945,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12011,7 +12000,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12066,7 +12055,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12121,7 +12110,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12177,7 +12166,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12232,11 +12221,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12246,7 +12235,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12271,7 +12260,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12296,7 +12285,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12321,7 +12310,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12348,10 +12337,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12374,7 +12363,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12395,7 +12384,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12452,7 +12441,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12509,7 +12498,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12566,7 +12555,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12623,7 +12612,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12680,7 +12669,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12739,7 +12728,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12796,7 +12785,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12853,7 +12842,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12910,7 +12899,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12967,7 +12956,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13025,7 +13014,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13082,7 +13071,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13108,7 +13097,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13132,7 +13121,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13189,18 +13178,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13256,7 +13245,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13312,7 +13301,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13367,7 +13356,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
@@ -13422,11 +13411,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13447,7 +13436,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13504,7 +13493,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13561,10 +13550,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13587,7 +13576,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13597,7 +13586,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13654,7 +13643,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13711,7 +13700,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13768,7 +13757,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13825,7 +13814,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13882,11 +13871,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13909,7 +13898,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -13966,7 +13955,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14023,7 +14012,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14050,18 +14039,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14113,7 +14102,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14165,11 +14154,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14223,7 +14212,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14278,7 +14267,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14332,7 +14321,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14388,7 +14377,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14445,7 +14434,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14464,7 +14453,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14487,7 +14476,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14508,7 +14497,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14566,45 +14555,45 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1251324106245051E-3</v>
+        <v>8.1945779867836892E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.492870874343775E-2</v>
+        <v>-2.5141774630133801E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.4239721373494119E-2</v>
+        <v>-7.4874248906600896E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.662252525803324E-2</v>
+        <v>-1.6764598123486515E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.0329553270402824E-2</v>
+        <v>3.058878022143191E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4673825463268433E-2</v>
+        <v>5.5141123116800639E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6285765113132768E-2</v>
+        <v>1.6424959686749289E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.4906879367343613E-3</v>
+        <v>-7.5547109105526039E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14623,38 +14612,38 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30987904518434572</v>
+        <v>-0.31252758403207515</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16441090166749858</v>
+        <v>-0.16581612304927207</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.1056089942728848E-3</v>
+        <v>-8.1748877036256443E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8179966099500309</v>
+        <v>-4.8591760681547322</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.26535883479479994</v>
+        <v>-0.26762685902381533</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.40128383372086074</v>
+        <v>-0.40471361007744927</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.52305563453068049</v>
+        <v>-0.52752619550957514</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14673,688 +14662,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15376,16 +15365,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15397,7 +15386,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15410,7 +15399,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15431,7 +15420,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15442,7 +15431,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15460,7 +15449,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15476,7 +15465,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15492,7 +15481,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15508,7 +15497,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15522,7 +15511,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15536,7 +15525,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15550,10 +15539,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15563,13 +15552,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15579,7 +15568,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15589,7 +15578,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15603,10 +15592,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15624,7 +15613,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15646,7 +15635,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15668,7 +15657,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15700,7 +15689,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15732,7 +15721,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15764,7 +15753,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15786,7 +15775,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15808,7 +15797,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15830,7 +15819,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15852,7 +15841,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15874,7 +15863,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15896,7 +15885,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15918,7 +15907,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -15950,7 +15939,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -15982,7 +15971,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16014,7 +16003,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16036,7 +16025,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16058,7 +16047,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16080,7 +16069,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16102,7 +16091,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16124,7 +16113,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16146,7 +16135,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16168,7 +16157,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16190,7 +16179,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16212,7 +16201,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16234,7 +16223,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16256,7 +16245,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16288,7 +16277,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16320,7 +16309,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16352,7 +16341,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16384,7 +16373,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16406,7 +16395,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16417,11 +16406,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16431,7 +16420,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>337941.38254475768</v>
@@ -16458,7 +16447,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16480,7 +16469,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16501,7 +16490,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16532,7 +16521,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16563,7 +16552,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16594,7 +16583,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16625,7 +16614,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16642,7 +16631,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16662,7 +16651,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.15</v>
@@ -16685,7 +16674,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16711,7 +16700,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16738,7 +16727,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16765,7 +16754,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16792,7 +16781,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16819,7 +16808,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16845,7 +16834,7 @@
         <v>2.6320130563932715</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16871,7 +16860,7 @@
         <v>2.9429407255351698</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16888,7 +16877,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16910,7 +16899,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16933,7 +16922,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16956,7 +16945,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16979,7 +16968,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17001,14 +16990,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17016,26 +17005,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17049,7 +17038,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17063,7 +17052,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17077,7 +17066,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17091,7 +17080,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17136,16 +17125,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>442</v>
       </c>
@@ -17157,7 +17146,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>441</v>
       </c>
@@ -17170,7 +17159,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>439</v>
       </c>
@@ -17191,7 +17180,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17202,7 +17191,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>440</v>
       </c>
@@ -17218,7 +17207,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>443</v>
       </c>
@@ -17232,10 +17221,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17245,13 +17234,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17261,7 +17250,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17271,7 +17260,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17285,10 +17274,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17306,7 +17295,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17328,7 +17317,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17350,7 +17339,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17372,7 +17361,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17394,7 +17383,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17416,7 +17405,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17438,7 +17427,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17460,7 +17449,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17482,7 +17471,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17504,7 +17493,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17526,7 +17515,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17548,7 +17537,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17570,7 +17559,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17592,7 +17581,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17614,7 +17603,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17636,7 +17625,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17658,7 +17647,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17680,7 +17669,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17702,7 +17691,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17724,7 +17713,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17746,7 +17735,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17768,7 +17757,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17790,7 +17779,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17812,7 +17801,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17834,7 +17823,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17856,7 +17845,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17878,7 +17867,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17900,7 +17889,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -17922,7 +17911,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -17944,7 +17933,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -17966,7 +17955,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -17988,7 +17977,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -17999,11 +17988,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18013,7 +18002,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>0</v>
@@ -18040,7 +18029,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18062,7 +18051,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18083,7 +18072,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18104,7 +18093,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18125,7 +18114,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18146,7 +18135,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18167,14 +18156,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18184,7 +18173,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>-0.15</v>
@@ -18207,7 +18196,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18233,7 +18222,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18260,7 +18249,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18287,7 +18276,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18314,7 +18303,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18341,7 +18330,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18367,7 +18356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18393,7 +18382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18410,7 +18399,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18432,7 +18421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18455,7 +18444,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18478,7 +18467,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18501,7 +18490,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18523,14 +18512,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18538,23 +18527,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18584,7 +18573,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18594,7 +18583,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18607,7 +18596,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18616,10 +18605,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18639,7 +18628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18648,7 +18637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18668,7 +18657,7 @@
         <v>2.1131011468081908</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18693,7 +18682,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18715,7 +18704,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18737,7 +18726,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18748,7 +18737,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>446</v>
       </c>
@@ -18762,7 +18751,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18781,7 +18770,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18799,7 +18788,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18810,7 +18799,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18819,7 +18808,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18827,7 +18816,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18839,24 +18828,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18865,7 +18854,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18880,7 +18869,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18889,7 +18878,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18901,7 +18890,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18912,7 +18901,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -18927,7 +18916,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -18938,7 +18927,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -18947,7 +18936,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -18959,7 +18948,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -18970,7 +18959,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -18985,7 +18974,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -18996,7 +18985,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19005,7 +18994,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19017,7 +19006,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19028,7 +19017,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19043,7 +19032,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19055,7 +19044,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19068,7 +19057,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19077,12 +19066,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19092,12 +19081,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19106,7 +19095,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19118,7 +19107,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19129,7 +19118,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19144,7 +19133,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19155,7 +19144,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19164,7 +19153,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19176,7 +19165,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19187,7 +19176,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19202,7 +19191,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19213,7 +19202,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19233,7 +19222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19242,7 +19231,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19250,7 +19239,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19263,7 +19252,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19275,7 +19264,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19291,7 +19280,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19299,7 +19288,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19309,7 +19298,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19321,7 +19310,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19331,7 +19320,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19347,7 +19336,7 @@
         <v>0.92818576618522131</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19356,12 +19345,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19371,7 +19360,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19384,12 +19373,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19398,7 +19387,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19410,7 +19399,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19420,7 +19409,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19440,45 +19429,45 @@
         <v>0.60887707393464918</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21435619529683625</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.21780608938756418</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19487,7 +19476,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19499,7 +19488,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19509,7 +19498,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19529,14 +19518,14 @@
         <v>0.44575713910823733</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19547,7 +19536,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19559,7 +19548,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19571,7 +19560,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19590,15 +19579,15 @@
         <v>0.19503943049039696</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>420</v>
       </c>
@@ -19607,7 +19596,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19617,7 +19606,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19627,7 +19616,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19646,16 +19635,16 @@
         <v>0.2819299041708756</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19663,7 +19652,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19671,7 +19660,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077A1AC5-7721-432B-870A-CD01D321C211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB28234-D0E3-4ABB-A1FD-BFB77FF5C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2673.4312191599997</v>
+        <v>2856.2299349999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21780608938756418</v>
+        <v>0.19125140052612388</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.1945779867836892E-3</v>
+        <v>7.6701249956295323E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1945779867836892E-3</v>
+        <v>7.6701249956295323E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.5141774630133801E-2</v>
+        <v>-2.3532701053805234E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.4874248906600896E-2</v>
+        <v>-7.0082296976578445E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.6764598123486515E-2</v>
+        <v>-1.5691663843583378E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.058878022143191E-2</v>
+        <v>2.8631098287260265E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5141123116800639E-2</v>
+        <v>5.1612091237325394E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6424959686749289E-2</v>
+        <v>1.5373762266797333E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.5547109105526039E-3</v>
+        <v>-7.0712094122772368E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.31252758403207515</v>
+        <v>-0.29252581865402233</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16581612304927207</v>
+        <v>-0.15520389117411865</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.1748877036256443E-3</v>
+        <v>-7.6516948905936038E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.8591760681547322</v>
+        <v>-4.548188799792829</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.26762685902381533</v>
+        <v>-0.25049874004629114</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.40471361007744927</v>
+        <v>-0.3788119390324925</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.52752619550957514</v>
+        <v>-0.49376451899696233</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.17</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21780608938756418</v>
+        <v>0.19125140052612388</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB28234-D0E3-4ABB-A1FD-BFB77FF5C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EC77CC-F0A0-4F79-BA9D-96E44EB0A7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2856.2299349999998</v>
+        <v>2787.6804165600001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19125140052612388</v>
+        <v>0.20093679634207984</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6701249956295323E-3</v>
+        <v>7.8587346266696025E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6701249956295323E-3</v>
+        <v>7.8587346266696025E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.3532701053805234E-2</v>
+        <v>-2.4111374030538153E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.0082296976578445E-2</v>
+        <v>-7.1805632148133652E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.5691663843583378E-2</v>
+        <v>-1.6077524429901003E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.8631098287260265E-2</v>
+        <v>2.9335141687766665E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.1612091237325394E-2</v>
+        <v>5.2881241021849795E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.5373762266797333E-2</v>
+        <v>1.5751805601226777E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.0712094122772368E-3</v>
+        <v>-7.2450916109397913E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.29252581865402233</v>
+        <v>-0.29971907648977697</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.15520389117411865</v>
+        <v>-0.15902038030135107</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-7.6516948905936038E-3</v>
+        <v>-7.8398513223295122E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.548188799792829</v>
+        <v>-4.660029507984456</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.25049874004629114</v>
+        <v>-0.25665854512939668</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.3788119390324925</v>
+        <v>-0.38812698671361939</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.49376451899696233</v>
+        <v>-0.50590626946410078</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.25</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19125140052612388</v>
+        <v>0.20093679634207984</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EC77CC-F0A0-4F79-BA9D-96E44EB0A7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5727A56A-8CB2-4794-9FC4-4259EAAE18B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>2787.6804165600001</v>
+        <v>3221.8273666799996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20093679634207984</v>
+        <v>0.14437156404012286</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.8587346266696025E-3</v>
+        <v>6.7997562017992307E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8587346266696025E-3</v>
+        <v>6.7997562017992307E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.4111374030538153E-2</v>
+        <v>-2.0862323629259962E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-7.1805632148133652E-2</v>
+        <v>-6.2129695901222026E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.6077524429901003E-2</v>
+        <v>-1.3911049506722855E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.9335141687766665E-2</v>
+        <v>2.538217933267754E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2881241021849795E-2</v>
+        <v>4.5755400033089894E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.5751805601226777E-2</v>
+        <v>1.3629221867728133E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-7.2450916109397913E-3</v>
+        <v>-6.2688026704585433E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.29971907648977697</v>
+        <v>-0.25933139951597728</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.15902038030135107</v>
+        <v>-0.13759210210471512</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-7.8398513223295122E-3</v>
+        <v>-6.783417456200003E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.660029507984456</v>
+        <v>-4.0320822693198837</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.25665854512939668</v>
+        <v>-0.22207335110486803</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.38812698671361939</v>
+        <v>-0.33582618708554302</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.50590626946410078</v>
+        <v>-0.43773450265688152</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.22</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20093679634207984</v>
+        <v>0.14437156404012286</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5727A56A-8CB2-4794-9FC4-4259EAAE18B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88951548-AFD7-4B6C-BFD3-BAA6A6F82B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3221.8273666799996</v>
+        <v>3747.3736747199996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14437156404012286</v>
+        <v>8.8158467557158948E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.7997562017992307E-3</v>
+        <v>5.8461318564249484E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7997562017992307E-3</v>
+        <v>5.8461318564249484E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-2.0862323629259962E-2</v>
+        <v>-1.7936509949546674E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-6.2129695901222026E-2</v>
+        <v>-5.3416384890684787E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.3911049506722855E-2</v>
+        <v>-1.1960109636877575E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.538217933267754E-2</v>
+        <v>2.182248345065569E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.5755400033089894E-2</v>
+        <v>3.9338484174790703E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.3629221867728133E-2</v>
+        <v>1.1717806605790651E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-6.2688026704585433E-3</v>
+        <v>-5.3896413203332596E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.25933139951597728</v>
+        <v>-0.2229617520228829</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.13759210210471512</v>
+        <v>-0.11829564876076118</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-6.783417456200003E-3</v>
+        <v>-5.8320845202695154E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.0320822693198837</v>
+        <v>-3.4666073169152662</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.22207335110486803</v>
+        <v>-0.19092891771820972</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.33582618708554302</v>
+        <v>-0.28872861206744854</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.43773450265688152</v>
+        <v>-0.37634490777207497</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.41</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14437156404012286</v>
+        <v>8.8158467557158948E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88951548-AFD7-4B6C-BFD3-BAA6A6F82B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C72022-8606-4272-A17F-C7BFAF0194AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3747.3736747199996</v>
+        <v>3998.7219089999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.8158467557158948E-2</v>
+        <v>6.486383811742602E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.8461318564249484E-3</v>
+        <v>5.4786607111639513E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.8461318564249484E-3</v>
+        <v>5.4786607111639513E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-1.7936509949546674E-2</v>
+        <v>-1.6809072181289453E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-5.3416384890684787E-2</v>
+        <v>-5.0058783554698887E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.1960109636877575E-2</v>
+        <v>-1.1208331316845271E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.182248345065569E-2</v>
+        <v>2.0450784490900188E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.9338484174790703E-2</v>
+        <v>3.6865779455232429E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.1717806605790651E-2</v>
+        <v>1.0981258761998096E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-5.3896413203332596E-3</v>
+        <v>-5.0508638659123115E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.2229617520228829</v>
+        <v>-0.20894701332430166</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.11829564876076118</v>
+        <v>-0.11085992226722761</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.8320845202695154E-3</v>
+        <v>-5.4654963504240026E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-3.4666073169152662</v>
+        <v>-3.2487062855663065</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.19092891771820972</v>
+        <v>-0.17892767146163652</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.28872861206744854</v>
+        <v>-0.27057995645178035</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.37634490777207497</v>
+        <v>-0.35268894214068736</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.64</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.8158467557158948E-2</v>
+        <v>6.486383811742602E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C72022-8606-4272-A17F-C7BFAF0194AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A29C044-1AD7-4A70-BDB9-BBFCF3C80D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3998.7219089999999</v>
+        <v>4272.9199827600005</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.486383811742602E-2</v>
+        <v>4.1580625733161458E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.4786607111639513E-3</v>
+        <v>5.127088900821879E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.4786607111639513E-3</v>
+        <v>5.127088900821879E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-1.6809072181289453E-2</v>
+        <v>-1.5730415142917939E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-5.0058783554698887E-2</v>
+        <v>-4.6846455198247615E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.1208331316845271E-2</v>
+        <v>-1.0489080109347177E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.0450784490900188E-2</v>
+        <v>1.9138434683997504E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6865779455232429E-2</v>
+        <v>3.4500060987516977E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.0981258761998096E-2</v>
+        <v>1.027657905534581E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-5.0508638659123115E-3</v>
+        <v>-4.7267442595436068E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.20894701332430166</v>
+        <v>-0.19553864883290262</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.11085992226722761</v>
+        <v>-0.10374591656023974</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.4654963504240026E-3</v>
+        <v>-5.1147693118941198E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-3.2487062855663065</v>
+        <v>-3.0402331549417303</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.17892767146163652</v>
+        <v>-0.16744568184912509</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.27057995645178035</v>
+        <v>-0.25321653678642547</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.35268894214068736</v>
+        <v>-0.33005649665572345</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.75</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.486383811742602E-2</v>
+        <v>4.1580625733161458E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A29C044-1AD7-4A70-BDB9-BBFCF3C80D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981A6869-E6DC-4F91-9990-75C48D392455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4272.9199827600005</v>
+        <v>3655.9743168</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>4.1580625733161458E-2</v>
+        <v>9.7151920584806817E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.127088900821879E-3</v>
+        <v>5.9922851528355714E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.127088900821879E-3</v>
+        <v>5.9922851528355714E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-1.5730415142917939E-2</v>
+        <v>-1.8384922698285341E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-4.6846455198247615E-2</v>
+        <v>-5.4751794512951903E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.0489080109347177E-2</v>
+        <v>-1.2259112377799513E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>1.9138434683997504E-2</v>
+        <v>2.2368045536922079E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4500060987516977E-2</v>
+        <v>4.0321946279160463E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.027657905534581E-2</v>
+        <v>1.2010751770935416E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-4.7267442595436068E-3</v>
+        <v>-5.5243823533415908E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.19553864883290262</v>
+        <v>-0.22853579582345493</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.10374591656023974</v>
+        <v>-0.12125303997978019</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.1147693118941198E-3</v>
+        <v>-5.9778866332762526E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-3.0402331549417303</v>
+        <v>-3.5532724998381475</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.16744568184912509</v>
+        <v>-0.19570214066116493</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.25321653678642547</v>
+        <v>-0.29594682736913475</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.33005649665572345</v>
+        <v>-0.38575353046637678</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.87</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>4.1580625733161458E-2</v>
+        <v>9.7151920584806817E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981A6869-E6DC-4F91-9990-75C48D392455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E53A7B8-BC55-4C95-BEA8-29323E32D2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3655.9743168</v>
+        <v>4021.5717484800002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.7151920584806817E-2</v>
+        <v>6.2843218767976605E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.9922851528355714E-3</v>
+        <v>5.4475319571232472E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9922851528355714E-3</v>
+        <v>5.4475319571232472E-3</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-1.8384922698285341E-2</v>
+        <v>-1.6713566089350308E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-5.4751794512951903E-2</v>
+        <v>-4.9774358648138096E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-1.2259112377799513E-2</v>
+        <v>-1.1144647616181377E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.2368045536922079E-2</v>
+        <v>2.0334586851747348E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.0321946279160463E-2</v>
+        <v>3.665631479923679E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.2010751770935416E-2</v>
+        <v>1.0918865246304924E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-5.5243823533415908E-3</v>
+        <v>-5.0221657757650827E-3</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14619,31 +14619,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.22853579582345493</v>
+        <v>-0.20775981438495905</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.12125303997978019</v>
+        <v>-0.11023003634525473</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.9778866332762526E-3</v>
+        <v>-5.4344423938875027E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-3.5532724998381475</v>
+        <v>-3.2302477271255889</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.19570214066116493</v>
+        <v>-0.1779110369646954</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.29594682736913475</v>
+        <v>-0.26904257033557705</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.38575353046637678</v>
+        <v>-0.35068502769670623</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-1.6</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.7151920584806817E-2</v>
+        <v>6.2843218767976605E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/9959.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9959.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E53A7B8-BC55-4C95-BEA8-29323E32D2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03B7D22-1B22-484A-9E55-CBC7932AF14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -2467,9 +2468,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3146,7 +3144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3891,6 +3889,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4220,10 +4222,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4235,18 +4237,18 @@
         <v>45786</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4260,7 +4262,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4269,10 +4271,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4286,7 +4288,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4296,7 +4298,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4309,20 +4311,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4338,17 +4340,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4362,7 +4364,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4388,35 +4390,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4424,7 +4426,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4434,26 +4436,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4474,7 +4476,7 @@
         <v>2.1131011468081908</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4487,7 +4489,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4498,7 +4500,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4506,7 +4508,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4517,7 +4519,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F29" s="302">
         <v>0.3674</v>
@@ -4525,7 +4527,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4536,7 +4538,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F30" s="312">
         <v>0.21740000000000001</v>
@@ -4544,7 +4546,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4555,7 +4557,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4563,7 +4565,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4574,7 +4576,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -4586,7 +4588,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4594,45 +4596,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4647,18 +4649,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4671,7 +4673,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4683,17 +4685,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4705,17 +4707,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4730,7 +4732,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4745,7 +4747,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4758,12 +4760,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4775,17 +4777,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4797,17 +4799,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4818,27 +4820,27 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4851,7 +4853,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4864,24 +4866,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>5.4475319571232472E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
+        <f>Normalized_FCF!C94</f>
         <v>0</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4890,73 +4892,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>3.7288355461672987E-3</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>3.1739188455256421E-3</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>2.8327145387125552E-2</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>2.4111564983485257E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.11998888979909481</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.11998888979909481</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.0970574812713703</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.0970574812713703</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4967,33 +4969,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5002,7 +5004,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5011,7 +5013,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5023,31 +5025,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5055,7 +5057,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5068,7 +5070,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5080,36 +5082,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5122,7 +5124,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5135,7 +5137,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5144,7 +5146,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5153,12 +5155,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5171,7 +5173,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5184,7 +5186,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_fa